--- a/output/exports/dma_recovery.xlsx
+++ b/output/exports/dma_recovery.xlsx
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="AO2" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP2" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AQ2" t="n">
         <v>-0.02758682377949483</v>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="AO3" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP3" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0.07410272783592398</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="AO4" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="AP4" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0.1984485748272413</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="AO5" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AP5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.6662873839712555</v>
@@ -1261,119 +1261,119 @@
         <v>24</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>246.8500061035156</v>
+        <v>336.6000061035156</v>
       </c>
       <c r="B6" t="n">
-        <v>255</v>
+        <v>340.9500122070312</v>
       </c>
       <c r="C6" t="n">
-        <v>242.4100036621094</v>
+        <v>336.6000061035156</v>
       </c>
       <c r="D6" t="n">
-        <v>251.1399993896484</v>
+        <v>339.0499877929688</v>
       </c>
       <c r="E6" t="n">
-        <v>179922</v>
+        <v>422556</v>
       </c>
       <c r="F6" t="n">
-        <v>246.9600067138672</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="G6" t="n">
-        <v>1.692578782857046</v>
+        <v>0.5188259897222824</v>
       </c>
       <c r="H6" t="n">
-        <v>233.5529991149902</v>
+        <v>336.4399963378906</v>
       </c>
       <c r="I6" t="n">
-        <v>230.4343994140625</v>
+        <v>336.9709985351562</v>
       </c>
       <c r="J6" t="n">
-        <v>234.2810997009277</v>
+        <v>337.8599990844726</v>
       </c>
       <c r="K6" t="n">
-        <v>241.5257498168945</v>
+        <v>328.0308988189697</v>
       </c>
       <c r="L6" t="n">
-        <v>241.5213329470449</v>
+        <v>338.1186828777073</v>
       </c>
       <c r="M6" t="n">
-        <v>236.5665923047616</v>
+        <v>337.2539068134053</v>
       </c>
       <c r="N6" t="n">
-        <v>233.3689664244175</v>
+        <v>336.5761006916337</v>
       </c>
       <c r="O6" t="n">
-        <v>83.651903015971</v>
+        <v>56.64061149582589</v>
       </c>
       <c r="P6" t="n">
-        <v>7.748571123395648</v>
+        <v>4.171439034598214</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.085359218852905</v>
+        <v>1.230331569026743</v>
       </c>
       <c r="R6" t="n">
-        <v>59715.05</v>
+        <v>289661.1</v>
       </c>
       <c r="S6" t="n">
-        <v>3.013009283254389</v>
+        <v>1.45879443252822</v>
       </c>
       <c r="T6" t="n">
-        <v>293.1099853515625</v>
+        <v>411.2999877929688</v>
       </c>
       <c r="U6" t="n">
-        <v>209.9600067138672</v>
+        <v>240.3999938964844</v>
       </c>
       <c r="V6" t="n">
-        <v>-14.31885232827341</v>
+        <v>-17.56625386440994</v>
       </c>
       <c r="W6" t="n">
-        <v>19.61325555294976</v>
+        <v>41.03577221343974</v>
       </c>
       <c r="X6" t="n">
-        <v>3.980631290884171</v>
+        <v>3.359161900196522</v>
       </c>
       <c r="Y6" t="b">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>225.1000061035156</v>
+        <v>332.8999938964844</v>
       </c>
       <c r="AA6" t="n">
-        <v>250.1900024414062</v>
+        <v>342.7999877929688</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Sideways</t>
+          <t>Uptrend</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>Near Breakout</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>SESHAPAPER</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>SESHAPAPER.NS</t>
+          <t>IIFLCAPS.NS</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Seshasayee Paper and Boards Limited</t>
+          <t>IIFL Capital Services Limited</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
@@ -1390,124 +1390,124 @@
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>Momentum Watch</t>
         </is>
       </c>
       <c r="AO6" t="n">
         <v>-5</v>
       </c>
       <c r="AP6" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.03648222708060733</v>
+        <v>0.6097567027088719</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
+          <t>Price is in an uptrend | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS6" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="AT6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>336.6000061035156</v>
+        <v>3297.199951171875</v>
       </c>
       <c r="B7" t="n">
-        <v>340.9500122070312</v>
+        <v>3319.800048828125</v>
       </c>
       <c r="C7" t="n">
-        <v>336.6000061035156</v>
+        <v>3210.10009765625</v>
       </c>
       <c r="D7" t="n">
-        <v>339.0499877929688</v>
+        <v>3302.39990234375</v>
       </c>
       <c r="E7" t="n">
-        <v>422556</v>
+        <v>43706</v>
       </c>
       <c r="F7" t="n">
-        <v>337.2999877929688</v>
+        <v>3297.199951171875</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5188259897222824</v>
+        <v>0.1577080931966846</v>
       </c>
       <c r="H7" t="n">
-        <v>336.4399963378906</v>
+        <v>3174.540002441406</v>
       </c>
       <c r="I7" t="n">
-        <v>336.9709985351562</v>
+        <v>3185.400004882812</v>
       </c>
       <c r="J7" t="n">
-        <v>337.8599990844726</v>
+        <v>3375.843996582031</v>
       </c>
       <c r="K7" t="n">
-        <v>328.0308988189697</v>
+        <v>3284.987001953125</v>
       </c>
       <c r="L7" t="n">
-        <v>338.1186828777073</v>
+        <v>3197.57092287815</v>
       </c>
       <c r="M7" t="n">
-        <v>337.2539068134053</v>
+        <v>3186.787082050515</v>
       </c>
       <c r="N7" t="n">
-        <v>336.5761006916337</v>
+        <v>3233.333477043682</v>
       </c>
       <c r="O7" t="n">
-        <v>56.64061149582589</v>
+        <v>69.18151020730613</v>
       </c>
       <c r="P7" t="n">
-        <v>4.171439034598214</v>
+        <v>83.73573521205357</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.230331569026743</v>
+        <v>2.535602522051475</v>
       </c>
       <c r="R7" t="n">
-        <v>289661.1</v>
+        <v>33932.55</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45879443252822</v>
+        <v>1.288025804132021</v>
       </c>
       <c r="T7" t="n">
-        <v>411.2999877929688</v>
+        <v>3925</v>
       </c>
       <c r="U7" t="n">
-        <v>240.3999938964844</v>
+        <v>2800.5</v>
       </c>
       <c r="V7" t="n">
-        <v>-17.56625386440994</v>
+        <v>-15.86242287022293</v>
       </c>
       <c r="W7" t="n">
-        <v>41.03577221343974</v>
+        <v>17.9217961915283</v>
       </c>
       <c r="X7" t="n">
-        <v>3.359161900196522</v>
+        <v>0.5300751686466956</v>
       </c>
       <c r="Y7" t="b">
         <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>332.8999938964844</v>
+        <v>3069.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>342.7999877929688</v>
+        <v>3324.699951171875</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Uptrend</t>
+          <t>Sideways</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>IIFLCAPS.NS</t>
+          <t>TIMKEN.NS</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>IIFL Capital Services Limited</t>
+          <t>Timken India Limited</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
@@ -1544,144 +1544,144 @@
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Momentum Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO7" t="n">
         <v>-3</v>
       </c>
       <c r="AP7" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.6097567027088719</v>
+        <v>0.09574949840559019</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Price is in an uptrend | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
+          <t>Strong positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS7" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="AT7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125.3000030517578</v>
+        <v>436</v>
       </c>
       <c r="B8" t="n">
-        <v>126.5</v>
+        <v>439.9500122070312</v>
       </c>
       <c r="C8" t="n">
-        <v>124</v>
+        <v>425.1000061035156</v>
       </c>
       <c r="D8" t="n">
-        <v>125.5</v>
+        <v>437.25</v>
       </c>
       <c r="E8" t="n">
-        <v>31941</v>
+        <v>91968</v>
       </c>
       <c r="F8" t="n">
-        <v>126.3099975585938</v>
+        <v>441.1499938964844</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6412774714986469</v>
+        <v>-0.884051671867303</v>
       </c>
       <c r="H8" t="n">
-        <v>123.2000003814697</v>
+        <v>414.8275024414062</v>
       </c>
       <c r="I8" t="n">
-        <v>124.6551998901367</v>
+        <v>437.9200006103516</v>
       </c>
       <c r="J8" t="n">
-        <v>124.1491998291016</v>
+        <v>421.8650006103516</v>
       </c>
       <c r="K8" t="n">
-        <v>124.3540998840332</v>
+        <v>422.3497496032715</v>
       </c>
       <c r="L8" t="n">
-        <v>124.0941910371286</v>
+        <v>422.1094401890283</v>
       </c>
       <c r="M8" t="n">
-        <v>123.8086498504301</v>
+        <v>420.3981616152403</v>
       </c>
       <c r="N8" t="n">
-        <v>123.8201072187077</v>
+        <v>424.6903972596593</v>
       </c>
       <c r="O8" t="n">
-        <v>59.46453745929973</v>
+        <v>64.67155691090414</v>
       </c>
       <c r="P8" t="n">
-        <v>3.902143205915178</v>
+        <v>12.18571254185268</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.109277454912493</v>
+        <v>2.786898237130401</v>
       </c>
       <c r="R8" t="n">
-        <v>15466.5</v>
+        <v>62240.05</v>
       </c>
       <c r="S8" t="n">
-        <v>2.065173116089613</v>
+        <v>1.477633774394461</v>
       </c>
       <c r="T8" t="n">
-        <v>159.9900054931641</v>
+        <v>701.5</v>
       </c>
       <c r="U8" t="n">
-        <v>93</v>
+        <v>331.7000122070312</v>
       </c>
       <c r="V8" t="n">
-        <v>-21.55760004310877</v>
+        <v>-37.66928011404134</v>
       </c>
       <c r="W8" t="n">
-        <v>34.94623655913978</v>
+        <v>31.82091766915266</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9214815732134356</v>
+        <v>3.527941098751649</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>119.4899978637695</v>
+        <v>397.2000122070312</v>
       </c>
       <c r="AA8" t="n">
-        <v>129.4900054931641</v>
+        <v>444.2999877929688</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Uptrend</t>
+          <t>Sideways</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Near Breakout</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>VRAJ</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>VRAJ.NS</t>
+          <t>TSFINV.NS</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Vraj Iron and Steel Limited</t>
+          <t>TSF INVESTMENTS LIMITED</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
@@ -1698,115 +1698,115 @@
       </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Momentum Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO8" t="n">
         <v>-3</v>
       </c>
       <c r="AP8" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.6638941888407768</v>
+        <v>0.1760297114049672</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>Price is in an uptrend | Positive momentum | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Strong positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS8" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="AT8" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3297.199951171875</v>
+        <v>246.8500061035156</v>
       </c>
       <c r="B9" t="n">
-        <v>3319.800048828125</v>
+        <v>255</v>
       </c>
       <c r="C9" t="n">
-        <v>3210.10009765625</v>
+        <v>242.4100036621094</v>
       </c>
       <c r="D9" t="n">
-        <v>3302.39990234375</v>
+        <v>251.1399993896484</v>
       </c>
       <c r="E9" t="n">
-        <v>43706</v>
+        <v>179922</v>
       </c>
       <c r="F9" t="n">
-        <v>3297.199951171875</v>
+        <v>246.9600067138672</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1577080931966846</v>
+        <v>1.692578782857046</v>
       </c>
       <c r="H9" t="n">
-        <v>3174.540002441406</v>
+        <v>233.5529991149902</v>
       </c>
       <c r="I9" t="n">
-        <v>3185.400004882812</v>
+        <v>230.4343994140625</v>
       </c>
       <c r="J9" t="n">
-        <v>3375.843996582031</v>
+        <v>234.2810997009277</v>
       </c>
       <c r="K9" t="n">
-        <v>3284.987001953125</v>
+        <v>241.5257498168945</v>
       </c>
       <c r="L9" t="n">
-        <v>3197.57092287815</v>
+        <v>241.5213329470449</v>
       </c>
       <c r="M9" t="n">
-        <v>3186.787082050515</v>
+        <v>236.5665923047616</v>
       </c>
       <c r="N9" t="n">
-        <v>3233.333477043682</v>
+        <v>233.3689664244175</v>
       </c>
       <c r="O9" t="n">
-        <v>69.18151020730613</v>
+        <v>83.651903015971</v>
       </c>
       <c r="P9" t="n">
-        <v>83.73573521205357</v>
+        <v>7.748571123395648</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.535602522051475</v>
+        <v>3.085359218852905</v>
       </c>
       <c r="R9" t="n">
-        <v>33932.55</v>
+        <v>59715.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.288025804132021</v>
+        <v>3.013009283254389</v>
       </c>
       <c r="T9" t="n">
-        <v>3925</v>
+        <v>293.1099853515625</v>
       </c>
       <c r="U9" t="n">
-        <v>2800.5</v>
+        <v>209.9600067138672</v>
       </c>
       <c r="V9" t="n">
-        <v>-15.86242287022293</v>
+        <v>-14.31885232827341</v>
       </c>
       <c r="W9" t="n">
-        <v>17.9217961915283</v>
+        <v>19.61325555294976</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5300751686466956</v>
+        <v>3.980631290884171</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>3069.5</v>
+        <v>225.1000061035156</v>
       </c>
       <c r="AA9" t="n">
-        <v>3324.699951171875</v>
+        <v>250.1900024414062</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1820,22 +1820,22 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Near Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>SESHAPAPER</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>TIMKEN.NS</t>
+          <t>SESHAPAPER.NS</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Timken India Limited</t>
+          <t>Seshasayee Paper and Boards Limited</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
@@ -1852,29 +1852,29 @@
       </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP9" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.09574949840559019</v>
+        <v>-0.03648222708060733</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>Strong positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS9" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="AT9" t="n">
         <v>67</v>
@@ -1882,114 +1882,114 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>436</v>
+        <v>125.3000030517578</v>
       </c>
       <c r="B10" t="n">
-        <v>439.9500122070312</v>
+        <v>126.5</v>
       </c>
       <c r="C10" t="n">
-        <v>425.1000061035156</v>
+        <v>124</v>
       </c>
       <c r="D10" t="n">
-        <v>437.25</v>
+        <v>125.5</v>
       </c>
       <c r="E10" t="n">
-        <v>91968</v>
+        <v>31941</v>
       </c>
       <c r="F10" t="n">
-        <v>441.1499938964844</v>
+        <v>126.3099975585938</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.884051671867303</v>
+        <v>-0.6412774714986469</v>
       </c>
       <c r="H10" t="n">
-        <v>414.8275024414062</v>
+        <v>123.2000003814697</v>
       </c>
       <c r="I10" t="n">
-        <v>437.9200006103516</v>
+        <v>124.6551998901367</v>
       </c>
       <c r="J10" t="n">
-        <v>421.8650006103516</v>
+        <v>124.1491998291016</v>
       </c>
       <c r="K10" t="n">
-        <v>422.3497496032715</v>
+        <v>124.3540998840332</v>
       </c>
       <c r="L10" t="n">
-        <v>422.1094401890283</v>
+        <v>124.0941910371286</v>
       </c>
       <c r="M10" t="n">
-        <v>420.3981616152403</v>
+        <v>123.8086498504301</v>
       </c>
       <c r="N10" t="n">
-        <v>424.6903972596593</v>
+        <v>123.8201072187077</v>
       </c>
       <c r="O10" t="n">
-        <v>64.67155691090414</v>
+        <v>59.46453745929973</v>
       </c>
       <c r="P10" t="n">
-        <v>12.18571254185268</v>
+        <v>3.902143205915178</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.786898237130401</v>
+        <v>3.109277454912493</v>
       </c>
       <c r="R10" t="n">
-        <v>62240.05</v>
+        <v>15466.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.477633774394461</v>
+        <v>2.065173116089613</v>
       </c>
       <c r="T10" t="n">
-        <v>701.5</v>
+        <v>159.9900054931641</v>
       </c>
       <c r="U10" t="n">
-        <v>331.7000122070312</v>
+        <v>93</v>
       </c>
       <c r="V10" t="n">
-        <v>-37.66928011404134</v>
+        <v>-21.55760004310877</v>
       </c>
       <c r="W10" t="n">
-        <v>31.82091766915266</v>
+        <v>34.94623655913978</v>
       </c>
       <c r="X10" t="n">
-        <v>3.527941098751649</v>
+        <v>0.9214815732134356</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>397.2000122070312</v>
+        <v>119.4899978637695</v>
       </c>
       <c r="AA10" t="n">
-        <v>444.2999877929688</v>
+        <v>129.4900054931641</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Sideways</t>
+          <t>Uptrend</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Near Breakout</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>VRAJ</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>TSFINV.NS</t>
+          <t>VRAJ.NS</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>TSF INVESTMENTS LIMITED</t>
+          <t>Vraj Iron and Steel Limited</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr"/>
@@ -2006,29 +2006,29 @@
       </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Momentum Watch</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="AP10" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.1760297114049672</v>
+        <v>0.6638941888407768</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>Strong positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
+          <t>Price is in an uptrend | Positive momentum | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS10" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="AT10" t="n">
         <v>67</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.3695653526003172</v>
@@ -2185,7 +2185,7 @@
         <v>86</v>
       </c>
       <c r="AT11" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AP12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.3904994419840191</v>
@@ -2339,7 +2339,7 @@
         <v>86</v>
       </c>
       <c r="AT12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AP13" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.4407132724262598</v>
@@ -2493,94 +2493,94 @@
         <v>86</v>
       </c>
       <c r="AT13" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22.97999954223633</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="B14" t="n">
-        <v>25.14999961853027</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="C14" t="n">
-        <v>22.30999946594238</v>
+        <v>32.36000061035156</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89999961853027</v>
+        <v>34.5099983215332</v>
       </c>
       <c r="E14" t="n">
-        <v>17663</v>
+        <v>173376</v>
       </c>
       <c r="F14" t="n">
-        <v>22.8700008392334</v>
+        <v>36.79000091552734</v>
       </c>
       <c r="G14" t="n">
-        <v>8.876251442083106</v>
+        <v>-6.197343129262755</v>
       </c>
       <c r="H14" t="n">
-        <v>23.17900009155273</v>
+        <v>32.24750013351441</v>
       </c>
       <c r="I14" t="n">
-        <v>23.27160007476807</v>
+        <v>32.71399993896485</v>
       </c>
       <c r="J14" t="n">
-        <v>25.94000007629394</v>
+        <v>33.55769990921021</v>
       </c>
       <c r="K14" t="n">
-        <v>26.16520003318787</v>
+        <v>33.32464998245239</v>
       </c>
       <c r="L14" t="n">
-        <v>23.36346857998252</v>
+        <v>33.20313188147026</v>
       </c>
       <c r="M14" t="n">
-        <v>23.21786681551761</v>
+        <v>32.70784632398362</v>
       </c>
       <c r="N14" t="n">
-        <v>23.72577093493368</v>
+        <v>32.84469960716838</v>
       </c>
       <c r="O14" t="n">
-        <v>64.62765478504912</v>
+        <v>67.12327756529518</v>
       </c>
       <c r="P14" t="n">
-        <v>1.531428473336356</v>
+        <v>2.22785758972168</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.150315248184525</v>
+        <v>6.455687331435085</v>
       </c>
       <c r="R14" t="n">
-        <v>4935.8</v>
+        <v>112079.95</v>
       </c>
       <c r="S14" t="n">
-        <v>3.57854856355606</v>
+        <v>1.546895765032015</v>
       </c>
       <c r="T14" t="n">
-        <v>42.75</v>
+        <v>46.34000015258789</v>
       </c>
       <c r="U14" t="n">
-        <v>19.29999923706055</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="V14" t="n">
-        <v>-41.75438685723913</v>
+        <v>-25.5287047736318</v>
       </c>
       <c r="W14" t="n">
-        <v>29.01554716497815</v>
+        <v>34.80467893474282</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.835431844789321</v>
+        <v>3.556971610219385</v>
       </c>
       <c r="Y14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>30.1200008392334</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.79999923706055</v>
+        <v>37.75</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Downtrend</t>
+          <t>Sideways</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2590,22 +2590,22 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>NAGREEKCAP</t>
+          <t>BIOFILCHEM</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>NAGREEKCAP.NS</t>
+          <t>BIOFILCHEM.NS</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure Limited</t>
+          <t>Biofil Chemicals &amp; Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr"/>
@@ -2622,115 +2622,115 @@
       </c>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.03448289469789895</v>
+        <v>0.7380418078894763</v>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
+          <t>Strong positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS14" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="AT14" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37.79999923706055</v>
+        <v>29.78000068664551</v>
       </c>
       <c r="B15" t="n">
-        <v>37.79999923706055</v>
+        <v>29.78000068664551</v>
       </c>
       <c r="C15" t="n">
-        <v>32.36000061035156</v>
+        <v>28.02000045776367</v>
       </c>
       <c r="D15" t="n">
-        <v>34.5099983215332</v>
+        <v>28.79999923706055</v>
       </c>
       <c r="E15" t="n">
-        <v>173376</v>
+        <v>5955</v>
       </c>
       <c r="F15" t="n">
-        <v>36.79000091552734</v>
+        <v>29.48999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.197343129262755</v>
+        <v>-2.339778024458949</v>
       </c>
       <c r="H15" t="n">
-        <v>32.24750013351441</v>
+        <v>28.01100006103515</v>
       </c>
       <c r="I15" t="n">
-        <v>32.71399993896485</v>
+        <v>28.85140003204346</v>
       </c>
       <c r="J15" t="n">
-        <v>33.55769990921021</v>
+        <v>29.66440000534057</v>
       </c>
       <c r="K15" t="n">
-        <v>33.32464998245239</v>
+        <v>28.38070001602173</v>
       </c>
       <c r="L15" t="n">
-        <v>33.20313188147026</v>
+        <v>28.68639257860127</v>
       </c>
       <c r="M15" t="n">
-        <v>32.70784632398362</v>
+        <v>28.41541374443018</v>
       </c>
       <c r="N15" t="n">
-        <v>32.84469960716838</v>
+        <v>28.67075673985033</v>
       </c>
       <c r="O15" t="n">
-        <v>67.12327756529518</v>
+        <v>61.4084456341049</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22785758972168</v>
+        <v>1.135714258466448</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.455687331435085</v>
+        <v>3.943452390807647</v>
       </c>
       <c r="R15" t="n">
-        <v>112079.95</v>
+        <v>3003.65</v>
       </c>
       <c r="S15" t="n">
-        <v>1.546895765032015</v>
+        <v>1.982587851447406</v>
       </c>
       <c r="T15" t="n">
-        <v>46.34000015258789</v>
+        <v>38.79999923706055</v>
       </c>
       <c r="U15" t="n">
-        <v>25.60000038146973</v>
+        <v>20</v>
       </c>
       <c r="V15" t="n">
-        <v>-25.5287047736318</v>
+        <v>-25.77319638307702</v>
       </c>
       <c r="W15" t="n">
-        <v>34.80467893474282</v>
+        <v>43.99999618530273</v>
       </c>
       <c r="X15" t="n">
-        <v>3.556971610219385</v>
+        <v>1.477409721402619</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>30.1200008392334</v>
+        <v>26.51000022888184</v>
       </c>
       <c r="AA15" t="n">
-        <v>37.75</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -2749,17 +2749,17 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>BIOFILCHEM</t>
+          <t>DAMODARIND</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>BIOFILCHEM.NS</t>
+          <t>DAMODARIND.NS</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals Limited</t>
+          <t>Damodar Industries Limited</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr"/>
@@ -2784,107 +2784,107 @@
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.7380418078894763</v>
+        <v>0.3930139369775091</v>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>Strong positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA</t>
+          <t>Strong positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS15" t="n">
         <v>125</v>
       </c>
       <c r="AT15" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>29.78000068664551</v>
+        <v>1548.099975585938</v>
       </c>
       <c r="B16" t="n">
-        <v>29.78000068664551</v>
+        <v>1624.699951171875</v>
       </c>
       <c r="C16" t="n">
-        <v>28.02000045776367</v>
+        <v>1530</v>
       </c>
       <c r="D16" t="n">
-        <v>28.79999923706055</v>
+        <v>1592.199951171875</v>
       </c>
       <c r="E16" t="n">
-        <v>5955</v>
+        <v>919086</v>
       </c>
       <c r="F16" t="n">
-        <v>29.48999977111816</v>
+        <v>1541.900024414062</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.339778024458949</v>
+        <v>3.262204161189186</v>
       </c>
       <c r="H16" t="n">
-        <v>28.01100006103515</v>
+        <v>1538.629998779297</v>
       </c>
       <c r="I16" t="n">
-        <v>28.85140003204346</v>
+        <v>1592.303996582031</v>
       </c>
       <c r="J16" t="n">
-        <v>29.66440000534057</v>
+        <v>1664.072999267578</v>
       </c>
       <c r="K16" t="n">
-        <v>28.38070001602173</v>
+        <v>1584.121497192383</v>
       </c>
       <c r="L16" t="n">
-        <v>28.68639257860127</v>
+        <v>1554.136411059851</v>
       </c>
       <c r="M16" t="n">
-        <v>28.41541374443018</v>
+        <v>1553.265245516916</v>
       </c>
       <c r="N16" t="n">
-        <v>28.67075673985033</v>
+        <v>1581.848856058459</v>
       </c>
       <c r="O16" t="n">
-        <v>61.4084456341049</v>
+        <v>58.44517996161747</v>
       </c>
       <c r="P16" t="n">
-        <v>1.135714258466448</v>
+        <v>56.7357177734375</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.943452390807647</v>
+        <v>3.563353819454614</v>
       </c>
       <c r="R16" t="n">
-        <v>3003.65</v>
+        <v>305350.65</v>
       </c>
       <c r="S16" t="n">
-        <v>1.982587851447406</v>
+        <v>3.00993628145216</v>
       </c>
       <c r="T16" t="n">
-        <v>38.79999923706055</v>
+        <v>1925</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>1057</v>
       </c>
       <c r="V16" t="n">
-        <v>-25.77319638307702</v>
+        <v>-17.28831422483766</v>
       </c>
       <c r="W16" t="n">
-        <v>43.99999618530273</v>
+        <v>50.63386482231551</v>
       </c>
       <c r="X16" t="n">
-        <v>1.477409721402619</v>
+        <v>0.5099642921209054</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>26.51000022888184</v>
+        <v>1478</v>
       </c>
       <c r="AA16" t="n">
-        <v>29.70000076293945</v>
+        <v>1645.699951171875</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2903,17 +2903,17 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>DAMODARIND</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>DAMODARIND.NS</t>
+          <t>ONESOURCE.NS</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Damodar Industries Limited</t>
+          <t>Onesource Specialty Pharma Limited</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.3930139369775091</v>
+        <v>0.468476557572959</v>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>Strong positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Positive momentum | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS16" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AT16" t="n">
         <v>107</v>
@@ -2960,85 +2960,85 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1548.099975585938</v>
+        <v>278.1499938964844</v>
       </c>
       <c r="B17" t="n">
-        <v>1624.699951171875</v>
+        <v>284.8999938964844</v>
       </c>
       <c r="C17" t="n">
-        <v>1530</v>
+        <v>274</v>
       </c>
       <c r="D17" t="n">
-        <v>1592.199951171875</v>
+        <v>283.0499877929688</v>
       </c>
       <c r="E17" t="n">
-        <v>919086</v>
+        <v>90543</v>
       </c>
       <c r="F17" t="n">
-        <v>1541.900024414062</v>
+        <v>276.75</v>
       </c>
       <c r="G17" t="n">
-        <v>3.262204161189186</v>
+        <v>2.276418353376242</v>
       </c>
       <c r="H17" t="n">
-        <v>1538.629998779297</v>
+        <v>281.7200012207031</v>
       </c>
       <c r="I17" t="n">
-        <v>1592.303996582031</v>
+        <v>281.3500006103516</v>
       </c>
       <c r="J17" t="n">
-        <v>1664.072999267578</v>
+        <v>283.7030010986328</v>
       </c>
       <c r="K17" t="n">
-        <v>1584.121497192383</v>
+        <v>282.239001159668</v>
       </c>
       <c r="L17" t="n">
-        <v>1554.136411059851</v>
+        <v>282.0839487067919</v>
       </c>
       <c r="M17" t="n">
-        <v>1553.265245516916</v>
+        <v>282.6243194823795</v>
       </c>
       <c r="N17" t="n">
-        <v>1581.848856058459</v>
+        <v>282.9721228270247</v>
       </c>
       <c r="O17" t="n">
-        <v>58.44517996161747</v>
+        <v>55.9369152330292</v>
       </c>
       <c r="P17" t="n">
-        <v>56.7357177734375</v>
+        <v>10.19642857142857</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.563353819454614</v>
+        <v>3.602341992993317</v>
       </c>
       <c r="R17" t="n">
-        <v>305350.65</v>
+        <v>29144.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.00993628145216</v>
+        <v>3.10670850439279</v>
       </c>
       <c r="T17" t="n">
-        <v>1925</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>1057</v>
+        <v>248</v>
       </c>
       <c r="V17" t="n">
-        <v>-17.28831422483766</v>
+        <v>-12.90769606370192</v>
       </c>
       <c r="W17" t="n">
-        <v>50.63386482231551</v>
+        <v>14.13305959393901</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5099642921209054</v>
+        <v>0.28734038526518</v>
       </c>
       <c r="Y17" t="b">
         <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1478</v>
+        <v>272</v>
       </c>
       <c r="AA17" t="n">
-        <v>1645.699951171875</v>
+        <v>296.8500061035156</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -3057,17 +3057,17 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>PRIMESECU</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ONESOURCE.NS</t>
+          <t>PRIMESECU.NS</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Onesource Specialty Pharma Limited</t>
+          <t>Prime Securities Limited</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr"/>
@@ -3092,13 +3092,13 @@
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.468476557572959</v>
+        <v>1.248871814983181</v>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
@@ -3109,119 +3109,119 @@
         <v>131</v>
       </c>
       <c r="AT17" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>278.1499938964844</v>
+        <v>22.97999954223633</v>
       </c>
       <c r="B18" t="n">
-        <v>284.8999938964844</v>
+        <v>25.14999961853027</v>
       </c>
       <c r="C18" t="n">
-        <v>274</v>
+        <v>22.30999946594238</v>
       </c>
       <c r="D18" t="n">
-        <v>283.0499877929688</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="E18" t="n">
-        <v>90543</v>
+        <v>17663</v>
       </c>
       <c r="F18" t="n">
-        <v>276.75</v>
+        <v>22.8700008392334</v>
       </c>
       <c r="G18" t="n">
-        <v>2.276418353376242</v>
+        <v>8.876251442083106</v>
       </c>
       <c r="H18" t="n">
-        <v>281.7200012207031</v>
+        <v>23.17900009155273</v>
       </c>
       <c r="I18" t="n">
-        <v>281.3500006103516</v>
+        <v>23.27160007476807</v>
       </c>
       <c r="J18" t="n">
-        <v>283.7030010986328</v>
+        <v>25.94000007629394</v>
       </c>
       <c r="K18" t="n">
-        <v>282.239001159668</v>
+        <v>26.16520003318787</v>
       </c>
       <c r="L18" t="n">
-        <v>282.0839487067919</v>
+        <v>23.36346857998252</v>
       </c>
       <c r="M18" t="n">
-        <v>282.6243194823795</v>
+        <v>23.21786681551761</v>
       </c>
       <c r="N18" t="n">
-        <v>282.9721228270247</v>
+        <v>23.72577093493368</v>
       </c>
       <c r="O18" t="n">
-        <v>55.9369152330292</v>
+        <v>64.62765478504912</v>
       </c>
       <c r="P18" t="n">
-        <v>10.19642857142857</v>
+        <v>1.531428473336356</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.602341992993317</v>
+        <v>6.150315248184525</v>
       </c>
       <c r="R18" t="n">
-        <v>29144.35</v>
+        <v>4935.8</v>
       </c>
       <c r="S18" t="n">
-        <v>3.10670850439279</v>
+        <v>3.57854856355606</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>42.75</v>
       </c>
       <c r="U18" t="n">
-        <v>248</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="V18" t="n">
-        <v>-12.90769606370192</v>
+        <v>-41.75438685723913</v>
       </c>
       <c r="W18" t="n">
-        <v>14.13305959393901</v>
+        <v>29.01554716497815</v>
       </c>
       <c r="X18" t="n">
-        <v>0.28734038526518</v>
+        <v>-4.835431844789321</v>
       </c>
       <c r="Y18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>272</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>296.8500061035156</v>
+        <v>24.79999923706055</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Sideways</t>
+          <t>Downtrend</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>PRIMESECU</t>
+          <t>NAGREEKCAP</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>PRIMESECU.NS</t>
+          <t>NAGREEKCAP.NS</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Prime Securities Limited</t>
+          <t>Nagreeka Capital &amp; Infrastructure Limited</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr"/>
@@ -3238,32 +3238,32 @@
       </c>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP18" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.248871814983181</v>
+        <v>-0.03448289469789895</v>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>Positive momentum | Volume is more than 2x average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
       <c r="AS18" t="n">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="AT18" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AP19" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.846153070235365</v>
@@ -3417,99 +3417,99 @@
         <v>131</v>
       </c>
       <c r="AT19" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>187.8000030517578</v>
+        <v>37.5</v>
       </c>
       <c r="B20" t="n">
-        <v>189</v>
+        <v>39.81999969482422</v>
       </c>
       <c r="C20" t="n">
-        <v>187.0500030517578</v>
+        <v>37</v>
       </c>
       <c r="D20" t="n">
-        <v>188.0299987792969</v>
+        <v>37.90999984741211</v>
       </c>
       <c r="E20" t="n">
-        <v>1118348</v>
+        <v>620683</v>
       </c>
       <c r="F20" t="n">
-        <v>188.0599975585938</v>
+        <v>36.61000061035156</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.01595170673525104</v>
+        <v>3.550940222309018</v>
       </c>
       <c r="H20" t="n">
-        <v>187.3750022888184</v>
+        <v>35.24149990081787</v>
       </c>
       <c r="I20" t="n">
-        <v>186.5714010620117</v>
+        <v>34.78519996643067</v>
       </c>
       <c r="J20" t="n">
-        <v>185.2993005371094</v>
+        <v>35.86910007476806</v>
       </c>
       <c r="K20" t="n">
-        <v>185.3836003112793</v>
+        <v>37.13745004653931</v>
       </c>
       <c r="L20" t="n">
-        <v>188.0789826866439</v>
+        <v>36.02839052260484</v>
       </c>
       <c r="M20" t="n">
-        <v>187.6537603196727</v>
+        <v>35.52854868001531</v>
       </c>
       <c r="N20" t="n">
-        <v>186.7953813526317</v>
+        <v>35.273816056426</v>
       </c>
       <c r="O20" t="n">
-        <v>55.12367395904943</v>
+        <v>76.86565942610204</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41499764578683</v>
+        <v>1.769285746983119</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.284368271799795</v>
+        <v>4.667068726205489</v>
       </c>
       <c r="R20" t="n">
-        <v>1840214.4</v>
+        <v>85157.14999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6077270126785227</v>
+        <v>7.288677462784981</v>
       </c>
       <c r="T20" t="n">
-        <v>210.75</v>
+        <v>53</v>
       </c>
       <c r="U20" t="n">
-        <v>170.1000061035156</v>
+        <v>26.52000045776367</v>
       </c>
       <c r="V20" t="n">
-        <v>-10.78054624944395</v>
+        <v>-28.47169840110923</v>
       </c>
       <c r="W20" t="n">
-        <v>10.54085363457884</v>
+        <v>42.94871490590054</v>
       </c>
       <c r="X20" t="n">
-        <v>1.427525662234401</v>
+        <v>2.080244604582897</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>184.1000061035156</v>
+        <v>33.59999847412109</v>
       </c>
       <c r="AA20" t="n">
-        <v>191.8000030517578</v>
+        <v>39.93999862670898</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Strong Uptrend</t>
+          <t>Sideways</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3519,17 +3519,17 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>HPAL</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>CASTROLIND.NS</t>
+          <t>HPAL.NS</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Castrol India Limited</t>
+          <t>HP Adhesives Limited</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr"/>
@@ -3546,124 +3546,124 @@
       </c>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Momentum Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO20" t="n">
         <v>-3</v>
       </c>
       <c r="AP20" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.959290406746494</v>
+        <v>0.4709972465152176</v>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Strong positive momentum | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS20" t="n">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="AT20" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>258.6000061035156</v>
+        <v>412.6000061035156</v>
       </c>
       <c r="B21" t="n">
-        <v>259</v>
+        <v>420</v>
       </c>
       <c r="C21" t="n">
-        <v>252</v>
+        <v>409.25</v>
       </c>
       <c r="D21" t="n">
-        <v>258.8999938964844</v>
+        <v>419</v>
       </c>
       <c r="E21" t="n">
-        <v>1192</v>
+        <v>15197483</v>
       </c>
       <c r="F21" t="n">
-        <v>256.8999938964844</v>
+        <v>416.5499877929688</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7785130585896027</v>
+        <v>0.5881676338564512</v>
       </c>
       <c r="H21" t="n">
-        <v>257.5319969177246</v>
+        <v>412.1425018310547</v>
       </c>
       <c r="I21" t="n">
-        <v>254.7721984863281</v>
+        <v>396.7459997558594</v>
       </c>
       <c r="J21" t="n">
-        <v>254.6146994018555</v>
+        <v>392.6270001220703</v>
       </c>
       <c r="K21" t="n">
-        <v>248.0404494476318</v>
+        <v>400.5447001647949</v>
       </c>
       <c r="L21" t="n">
-        <v>258.3104603485323</v>
+        <v>418.0699956865499</v>
       </c>
       <c r="M21" t="n">
-        <v>257.8832714234509</v>
+        <v>413.0015399112719</v>
       </c>
       <c r="N21" t="n">
-        <v>255.8831547182216</v>
+        <v>403.114517743576</v>
       </c>
       <c r="O21" t="n">
-        <v>56.13921641713981</v>
+        <v>65.71170661179153</v>
       </c>
       <c r="P21" t="n">
-        <v>7.125001089913504</v>
+        <v>7.264288766043527</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.752028295822318</v>
+        <v>1.733720469222799</v>
       </c>
       <c r="R21" t="n">
-        <v>2389.25</v>
+        <v>12249727.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4989013288688919</v>
+        <v>1.240638485402352</v>
       </c>
       <c r="T21" t="n">
-        <v>307</v>
+        <v>453.2000122070312</v>
       </c>
       <c r="U21" t="n">
-        <v>191</v>
+        <v>345.5</v>
       </c>
       <c r="V21" t="n">
-        <v>-15.66775443111258</v>
+        <v>-7.546339648245192</v>
       </c>
       <c r="W21" t="n">
-        <v>35.54973502433737</v>
+        <v>21.27351664254703</v>
       </c>
       <c r="X21" t="n">
-        <v>4.378134482918398</v>
+        <v>4.607550624839647</v>
       </c>
       <c r="Y21" t="b">
         <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>251.6999969482422</v>
+        <v>386.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>265</v>
+        <v>429.1000061035156</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Strong Uptrend</t>
+          <t>Sideways</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>NAHARCAP</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>NAHARCAP.NS</t>
+          <t>KOTAKBANK.NS</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Nahar Capital and Financial Services Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr"/>
@@ -3700,124 +3700,124 @@
       </c>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Momentum Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO21" t="n">
         <v>-3</v>
       </c>
       <c r="AP21" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.8472234290328254</v>
+        <v>0.3131784838299418</v>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA</t>
+          <t>Strong positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS21" t="n">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="AT21" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>37.5</v>
+        <v>187.8000030517578</v>
       </c>
       <c r="B22" t="n">
-        <v>39.81999969482422</v>
+        <v>189</v>
       </c>
       <c r="C22" t="n">
-        <v>37</v>
+        <v>187.0500030517578</v>
       </c>
       <c r="D22" t="n">
-        <v>37.90999984741211</v>
+        <v>188.0299987792969</v>
       </c>
       <c r="E22" t="n">
-        <v>620683</v>
+        <v>1118348</v>
       </c>
       <c r="F22" t="n">
-        <v>36.61000061035156</v>
+        <v>188.0599975585938</v>
       </c>
       <c r="G22" t="n">
-        <v>3.550940222309018</v>
+        <v>-0.01595170673525104</v>
       </c>
       <c r="H22" t="n">
-        <v>35.24149990081787</v>
+        <v>187.3750022888184</v>
       </c>
       <c r="I22" t="n">
-        <v>34.78519996643067</v>
+        <v>186.5714010620117</v>
       </c>
       <c r="J22" t="n">
-        <v>35.86910007476806</v>
+        <v>185.2993005371094</v>
       </c>
       <c r="K22" t="n">
-        <v>37.13745004653931</v>
+        <v>185.3836003112793</v>
       </c>
       <c r="L22" t="n">
-        <v>36.02839052260484</v>
+        <v>188.0789826866439</v>
       </c>
       <c r="M22" t="n">
-        <v>35.52854868001531</v>
+        <v>187.6537603196727</v>
       </c>
       <c r="N22" t="n">
-        <v>35.273816056426</v>
+        <v>186.7953813526317</v>
       </c>
       <c r="O22" t="n">
-        <v>76.86565942610204</v>
+        <v>55.12367395904943</v>
       </c>
       <c r="P22" t="n">
-        <v>1.769285746983119</v>
+        <v>2.41499764578683</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.667068726205489</v>
+        <v>1.284368271799795</v>
       </c>
       <c r="R22" t="n">
-        <v>85157.14999999999</v>
+        <v>1840214.4</v>
       </c>
       <c r="S22" t="n">
-        <v>7.288677462784981</v>
+        <v>0.6077270126785227</v>
       </c>
       <c r="T22" t="n">
-        <v>53</v>
+        <v>210.75</v>
       </c>
       <c r="U22" t="n">
-        <v>26.52000045776367</v>
+        <v>170.1000061035156</v>
       </c>
       <c r="V22" t="n">
-        <v>-28.47169840110923</v>
+        <v>-10.78054624944395</v>
       </c>
       <c r="W22" t="n">
-        <v>42.94871490590054</v>
+        <v>10.54085363457884</v>
       </c>
       <c r="X22" t="n">
-        <v>2.080244604582897</v>
+        <v>1.427525662234401</v>
       </c>
       <c r="Y22" t="b">
         <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>33.59999847412109</v>
+        <v>184.1000061035156</v>
       </c>
       <c r="AA22" t="n">
-        <v>39.93999862670898</v>
+        <v>191.8000030517578</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Sideways</t>
+          <t>Strong Uptrend</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3827,17 +3827,17 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>HPAL</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>HPAL.NS</t>
+          <t>CASTROLIND.NS</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>HP Adhesives Limited</t>
+          <t>Castrol India Limited</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr"/>
@@ -3854,124 +3854,124 @@
       </c>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Momentum Watch</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="AP22" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.4709972465152176</v>
+        <v>0.959290406746494</v>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>Strong positive momentum | Volume is more than 2x average | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS22" t="n">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="AT22" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>412.6000061035156</v>
+        <v>258.6000061035156</v>
       </c>
       <c r="B23" t="n">
-        <v>420</v>
+        <v>259</v>
       </c>
       <c r="C23" t="n">
-        <v>409.25</v>
+        <v>252</v>
       </c>
       <c r="D23" t="n">
-        <v>419</v>
+        <v>258.8999938964844</v>
       </c>
       <c r="E23" t="n">
-        <v>15197483</v>
+        <v>1192</v>
       </c>
       <c r="F23" t="n">
-        <v>416.5499877929688</v>
+        <v>256.8999938964844</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5881676338564512</v>
+        <v>0.7785130585896027</v>
       </c>
       <c r="H23" t="n">
-        <v>412.1425018310547</v>
+        <v>257.5319969177246</v>
       </c>
       <c r="I23" t="n">
-        <v>396.7459997558594</v>
+        <v>254.7721984863281</v>
       </c>
       <c r="J23" t="n">
-        <v>392.6270001220703</v>
+        <v>254.6146994018555</v>
       </c>
       <c r="K23" t="n">
-        <v>400.5447001647949</v>
+        <v>248.0404494476318</v>
       </c>
       <c r="L23" t="n">
-        <v>418.0699956865499</v>
+        <v>258.3104603485323</v>
       </c>
       <c r="M23" t="n">
-        <v>413.0015399112719</v>
+        <v>257.8832714234509</v>
       </c>
       <c r="N23" t="n">
-        <v>403.114517743576</v>
+        <v>255.8831547182216</v>
       </c>
       <c r="O23" t="n">
-        <v>65.71170661179153</v>
+        <v>56.13921641713981</v>
       </c>
       <c r="P23" t="n">
-        <v>7.264288766043527</v>
+        <v>7.125001089913504</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.733720469222799</v>
+        <v>2.752028295822318</v>
       </c>
       <c r="R23" t="n">
-        <v>12249727.2</v>
+        <v>2389.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.240638485402352</v>
+        <v>0.4989013288688919</v>
       </c>
       <c r="T23" t="n">
-        <v>453.2000122070312</v>
+        <v>307</v>
       </c>
       <c r="U23" t="n">
-        <v>345.5</v>
+        <v>191</v>
       </c>
       <c r="V23" t="n">
-        <v>-7.546339648245192</v>
+        <v>-15.66775443111258</v>
       </c>
       <c r="W23" t="n">
-        <v>21.27351664254703</v>
+        <v>35.54973502433737</v>
       </c>
       <c r="X23" t="n">
-        <v>4.607550624839647</v>
+        <v>4.378134482918398</v>
       </c>
       <c r="Y23" t="b">
         <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>386.75</v>
+        <v>251.6999969482422</v>
       </c>
       <c r="AA23" t="n">
-        <v>429.1000061035156</v>
+        <v>265</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Sideways</t>
+          <t>Strong Uptrend</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3981,17 +3981,17 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NAHARCAP</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>KOTAKBANK.NS</t>
+          <t>NAHARCAP.NS</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>Nahar Capital and Financial Services Limited</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr"/>
@@ -4008,32 +4008,32 @@
       </c>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Momentum Watch</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="AP23" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.3131784838299418</v>
+        <v>0.8472234290328254</v>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>Strong positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA</t>
+          <t>Strong price trend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS23" t="n">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="AT23" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24">
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP24" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.2442130508573356</v>
@@ -4187,119 +4187,119 @@
         <v>196</v>
       </c>
       <c r="AT24" t="n">
-        <v>191</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>209.8999938964844</v>
+        <v>15.97999954223633</v>
       </c>
       <c r="B25" t="n">
-        <v>225.7599945068359</v>
+        <v>17.29999923706055</v>
       </c>
       <c r="C25" t="n">
-        <v>200</v>
+        <v>15.60000038146973</v>
       </c>
       <c r="D25" t="n">
-        <v>221.1499938964844</v>
+        <v>16.1299991607666</v>
       </c>
       <c r="E25" t="n">
-        <v>431750</v>
+        <v>420547</v>
       </c>
       <c r="F25" t="n">
-        <v>210.1600036621094</v>
+        <v>15.97999954223633</v>
       </c>
       <c r="G25" t="n">
-        <v>5.22934432949691</v>
+        <v>0.9386709813965499</v>
       </c>
       <c r="H25" t="n">
-        <v>207.3924995422363</v>
+        <v>16.23850002288818</v>
       </c>
       <c r="I25" t="n">
-        <v>220.6941989135742</v>
+        <v>16.0468000793457</v>
       </c>
       <c r="J25" t="n">
-        <v>230.0062995910644</v>
+        <v>16.20920000076294</v>
       </c>
       <c r="K25" t="n">
-        <v>234.9700498199463</v>
+        <v>15.83925003528595</v>
       </c>
       <c r="L25" t="n">
-        <v>211.102954481969</v>
+        <v>16.36359902962491</v>
       </c>
       <c r="M25" t="n">
-        <v>210.6562489849827</v>
+        <v>16.27156977850234</v>
       </c>
       <c r="N25" t="n">
-        <v>217.4850292722071</v>
+        <v>16.14717708920056</v>
       </c>
       <c r="O25" t="n">
-        <v>70.55051367402692</v>
+        <v>51.96373273158718</v>
       </c>
       <c r="P25" t="n">
-        <v>9.67499760219029</v>
+        <v>0.9028568267822266</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.374857729690443</v>
+        <v>5.597376774688667</v>
       </c>
       <c r="R25" t="n">
-        <v>153400.3</v>
+        <v>220225.45</v>
       </c>
       <c r="S25" t="n">
-        <v>2.814531653458305</v>
+        <v>1.909620345877372</v>
       </c>
       <c r="T25" t="n">
-        <v>314.7000122070312</v>
+        <v>22.46999931335449</v>
       </c>
       <c r="U25" t="n">
-        <v>186</v>
+        <v>12</v>
       </c>
       <c r="V25" t="n">
-        <v>-29.7267285293282</v>
+        <v>-28.21539985014538</v>
       </c>
       <c r="W25" t="n">
-        <v>18.89784618090558</v>
+        <v>34.41665967305501</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.881624459820307</v>
+        <v>1.835624318278543</v>
       </c>
       <c r="Y25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>197.1300048828125</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="AA25" t="n">
-        <v>219.7899932861328</v>
+        <v>17.5</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Downtrend</t>
+          <t>Uptrend</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>ALLTIME</t>
+          <t>BLBLIMITED</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>ALLTIME.NS</t>
+          <t>BLBLIMITED.NS</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>All Time Plastics Limited</t>
+          <t>BLB Limited</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr"/>
@@ -4316,119 +4316,119 @@
       </c>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP25" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-0.056619535070456</v>
+        <v>0.8954260995312656</v>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is below 200 DMA</t>
+          <t>Price is in an uptrend | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS25" t="n">
-        <v>143</v>
+        <v>207</v>
       </c>
       <c r="AT25" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28.59000015258789</v>
+        <v>754.5499877929688</v>
       </c>
       <c r="B26" t="n">
-        <v>32.38999938964844</v>
+        <v>766.5</v>
       </c>
       <c r="C26" t="n">
-        <v>28.43000030517578</v>
+        <v>741</v>
       </c>
       <c r="D26" t="n">
-        <v>31.89999961853027</v>
+        <v>756.0999755859375</v>
       </c>
       <c r="E26" t="n">
-        <v>1039887</v>
+        <v>1619515</v>
       </c>
       <c r="F26" t="n">
-        <v>28.61000061035156</v>
+        <v>762.1500244140625</v>
       </c>
       <c r="G26" t="n">
-        <v>11.49947199577597</v>
+        <v>-0.7938133745749365</v>
       </c>
       <c r="H26" t="n">
-        <v>29.5210000038147</v>
+        <v>728.6250061035156</v>
       </c>
       <c r="I26" t="n">
-        <v>29.81320007324219</v>
+        <v>726.6460034179687</v>
       </c>
       <c r="J26" t="n">
-        <v>30.95860004425049</v>
+        <v>723.8510046386718</v>
       </c>
       <c r="K26" t="n">
-        <v>33.4475001335144</v>
+        <v>748.9362521362305</v>
       </c>
       <c r="L26" t="n">
-        <v>29.88815893587988</v>
+        <v>746.3303543482309</v>
       </c>
       <c r="M26" t="n">
-        <v>29.75932317140746</v>
+        <v>735.6683722028531</v>
       </c>
       <c r="N26" t="n">
-        <v>30.01706050052726</v>
+        <v>728.1269547543066</v>
       </c>
       <c r="O26" t="n">
-        <v>74.39799411549839</v>
+        <v>70.40623936492568</v>
       </c>
       <c r="P26" t="n">
-        <v>1.074999945504325</v>
+        <v>21.44285365513393</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.369905825578356</v>
+        <v>2.83598126537656</v>
       </c>
       <c r="R26" t="n">
-        <v>213049.95</v>
+        <v>862033.75</v>
       </c>
       <c r="S26" t="n">
-        <v>4.880953973469602</v>
+        <v>1.878714145472843</v>
       </c>
       <c r="T26" t="n">
-        <v>55.90000152587891</v>
+        <v>884</v>
       </c>
       <c r="U26" t="n">
-        <v>25.38999938964844</v>
+        <v>652.25</v>
       </c>
       <c r="V26" t="n">
-        <v>-42.93381261579722</v>
+        <v>-14.46832855362698</v>
       </c>
       <c r="W26" t="n">
-        <v>25.64001727206019</v>
+        <v>15.92180537921618</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.626655232250179</v>
+        <v>0.9565197878021771</v>
       </c>
       <c r="Y26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>27.60000038146973</v>
+        <v>696.0499877929688</v>
       </c>
       <c r="AA26" t="n">
-        <v>31.29999923706055</v>
+        <v>794</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Downtrend</t>
+          <t>Sideways</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4438,22 +4438,22 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Confirmed Breakout</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>TRACXN</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>TRACXN.NS</t>
+          <t>JSL.NS</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>Tracxn Technologies Limited</t>
+          <t>Jindal Stainless Limited</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr"/>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>Strong Breakout Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="AP26" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-0.1395349971922049</v>
+        <v>0.6311412509312818</v>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is below 200 DMA</t>
+          <t>Strong positive momentum | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS26" t="n">
-        <v>143</v>
+        <v>207</v>
       </c>
       <c r="AT26" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27">
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AP27" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.016620347866517</v>
@@ -4649,99 +4649,99 @@
         <v>196</v>
       </c>
       <c r="AT27" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>15.97999954223633</v>
+        <v>76</v>
       </c>
       <c r="B28" t="n">
-        <v>17.29999923706055</v>
+        <v>79.44000244140625</v>
       </c>
       <c r="C28" t="n">
-        <v>15.60000038146973</v>
+        <v>74.51999664306641</v>
       </c>
       <c r="D28" t="n">
-        <v>16.1299991607666</v>
+        <v>79</v>
       </c>
       <c r="E28" t="n">
-        <v>420547</v>
+        <v>273519</v>
       </c>
       <c r="F28" t="n">
-        <v>15.97999954223633</v>
+        <v>76.47000122070312</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9386709813965499</v>
+        <v>3.308485339231182</v>
       </c>
       <c r="H28" t="n">
-        <v>16.23850002288818</v>
+        <v>77.44099998474121</v>
       </c>
       <c r="I28" t="n">
-        <v>16.0468000793457</v>
+        <v>76.30499954223633</v>
       </c>
       <c r="J28" t="n">
-        <v>16.20920000076294</v>
+        <v>72.76809978485107</v>
       </c>
       <c r="K28" t="n">
-        <v>15.83925003528595</v>
+        <v>76.90024997711181</v>
       </c>
       <c r="L28" t="n">
-        <v>16.36359902962491</v>
+        <v>78.12538706711125</v>
       </c>
       <c r="M28" t="n">
-        <v>16.27156977850234</v>
+        <v>77.67786143301645</v>
       </c>
       <c r="N28" t="n">
-        <v>16.14717708920056</v>
+        <v>76.03386523820583</v>
       </c>
       <c r="O28" t="n">
-        <v>51.96373273158718</v>
+        <v>58.26559229335916</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9028568267822266</v>
+        <v>2.765001569475447</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.597376774688667</v>
+        <v>3.50000198667778</v>
       </c>
       <c r="R28" t="n">
-        <v>220225.45</v>
+        <v>201608.45</v>
       </c>
       <c r="S28" t="n">
-        <v>1.909620345877372</v>
+        <v>1.356684206440752</v>
       </c>
       <c r="T28" t="n">
-        <v>22.46999931335449</v>
+        <v>120</v>
       </c>
       <c r="U28" t="n">
-        <v>12</v>
+        <v>56.97000122070312</v>
       </c>
       <c r="V28" t="n">
-        <v>-28.21539985014538</v>
+        <v>-34.16666666666666</v>
       </c>
       <c r="W28" t="n">
-        <v>34.41665967305501</v>
+        <v>38.6694721910785</v>
       </c>
       <c r="X28" t="n">
-        <v>1.835624318278543</v>
+        <v>2.730485302080482</v>
       </c>
       <c r="Y28" t="b">
         <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>14.60000038146973</v>
+        <v>73</v>
       </c>
       <c r="AA28" t="n">
-        <v>17.5</v>
+        <v>81</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Uptrend</t>
+          <t>Sideways</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>BLBLIMITED</t>
+          <t>ARIHANTCAP</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>BLBLIMITED.NS</t>
+          <t>ARIHANTCAP.NS</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>BLB Limited</t>
+          <t>Arihant Capital Markets Limited</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr"/>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
@@ -4786,116 +4786,116 @@
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP28" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.8954260995312656</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>Price is in an uptrend | Strong volume confirmation | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS28" t="n">
-        <v>207</v>
+        <v>291</v>
       </c>
       <c r="AT28" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>754.5499877929688</v>
+        <v>43.36000061035156</v>
       </c>
       <c r="B29" t="n">
-        <v>766.5</v>
+        <v>43.83000183105469</v>
       </c>
       <c r="C29" t="n">
-        <v>741</v>
+        <v>42.45999908447266</v>
       </c>
       <c r="D29" t="n">
-        <v>756.0999755859375</v>
+        <v>43.65999984741211</v>
       </c>
       <c r="E29" t="n">
-        <v>1619515</v>
+        <v>3568740</v>
       </c>
       <c r="F29" t="n">
-        <v>762.1500244140625</v>
+        <v>43.86000061035156</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7938133745749365</v>
+        <v>-0.4559980851715939</v>
       </c>
       <c r="H29" t="n">
-        <v>728.6250061035156</v>
+        <v>43.40800037384033</v>
       </c>
       <c r="I29" t="n">
-        <v>726.6460034179687</v>
+        <v>43.35360031127929</v>
       </c>
       <c r="J29" t="n">
-        <v>723.8510046386718</v>
+        <v>44.25790016174317</v>
       </c>
       <c r="K29" t="n">
-        <v>748.9362521362305</v>
+        <v>42.34000011444092</v>
       </c>
       <c r="L29" t="n">
-        <v>746.3303543482309</v>
+        <v>44.53692680048745</v>
       </c>
       <c r="M29" t="n">
-        <v>735.6683722028531</v>
+        <v>44.12486400386921</v>
       </c>
       <c r="N29" t="n">
-        <v>728.1269547543066</v>
+        <v>43.79645011516082</v>
       </c>
       <c r="O29" t="n">
-        <v>70.40623936492568</v>
+        <v>61.90769181652171</v>
       </c>
       <c r="P29" t="n">
-        <v>21.44285365513393</v>
+        <v>1.961429050990513</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.83598126537656</v>
+        <v>4.49250814898199</v>
       </c>
       <c r="R29" t="n">
-        <v>862033.75</v>
+        <v>13228506</v>
       </c>
       <c r="S29" t="n">
-        <v>1.878714145472843</v>
+        <v>0.2697764963027571</v>
       </c>
       <c r="T29" t="n">
-        <v>884</v>
+        <v>53.75</v>
       </c>
       <c r="U29" t="n">
-        <v>652.25</v>
+        <v>33.0099983215332</v>
       </c>
       <c r="V29" t="n">
-        <v>-14.46832855362698</v>
+        <v>-18.77209330714026</v>
       </c>
       <c r="W29" t="n">
-        <v>15.92180537921618</v>
+        <v>32.26295688398039</v>
       </c>
       <c r="X29" t="n">
-        <v>0.9565197878021771</v>
+        <v>3.117618633451486</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>696.0499877929688</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="AA29" t="n">
-        <v>794</v>
+        <v>49.40000152587891</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Sideways</t>
+          <t>Strong Uptrend</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -4905,17 +4905,17 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>NSLNISP</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>JSL.NS</t>
+          <t>NSLNISP.NS</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>Jindal Stainless Limited</t>
+          <t>NMDC Steel Limited</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr"/>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -4940,107 +4940,99 @@
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP29" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.6311412509312818</v>
+        <v>1.31651396214001</v>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>Strong positive momentum | Strong volume confirmation | RSI indicates overbought conditions | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Strong price trend | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS29" t="n">
-        <v>207</v>
+        <v>291</v>
       </c>
       <c r="AT29" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>76</v>
+        <v>4158</v>
       </c>
       <c r="B30" t="n">
-        <v>79.44000244140625</v>
+        <v>4189</v>
       </c>
       <c r="C30" t="n">
-        <v>74.51999664306641</v>
+        <v>4084</v>
       </c>
       <c r="D30" t="n">
-        <v>79</v>
+        <v>4174.39990234375</v>
       </c>
       <c r="E30" t="n">
-        <v>273519</v>
+        <v>17556</v>
       </c>
       <c r="F30" t="n">
-        <v>76.47000122070312</v>
+        <v>4158.60009765625</v>
       </c>
       <c r="G30" t="n">
-        <v>3.308485339231182</v>
+        <v>0.3799308497204335</v>
       </c>
       <c r="H30" t="n">
-        <v>77.44099998474121</v>
+        <v>4018.929992675781</v>
       </c>
       <c r="I30" t="n">
-        <v>76.30499954223633</v>
+        <v>4247.118017578125</v>
       </c>
       <c r="J30" t="n">
-        <v>72.76809978485107</v>
+        <v>4293.671003417969</v>
       </c>
       <c r="K30" t="n">
-        <v>76.90024997711181</v>
+        <v>4097.059989013672</v>
       </c>
       <c r="L30" t="n">
-        <v>78.12538706711125</v>
+        <v>4117.276088764583</v>
       </c>
       <c r="M30" t="n">
-        <v>77.67786143301645</v>
+        <v>4109.577045023469</v>
       </c>
       <c r="N30" t="n">
-        <v>76.03386523820583</v>
+        <v>4186.058586926075</v>
       </c>
       <c r="O30" t="n">
-        <v>58.26559229335916</v>
+        <v>68.60669434597848</v>
       </c>
       <c r="P30" t="n">
-        <v>2.765001569475447</v>
+        <v>115.6857038225446</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.50000198667778</v>
+        <v>2.771313399025138</v>
       </c>
       <c r="R30" t="n">
-        <v>201608.45</v>
+        <v>19418.45</v>
       </c>
       <c r="S30" t="n">
-        <v>1.356684206440752</v>
-      </c>
-      <c r="T30" t="n">
-        <v>120</v>
-      </c>
-      <c r="U30" t="n">
-        <v>56.97000122070312</v>
-      </c>
-      <c r="V30" t="n">
-        <v>-34.16666666666666</v>
-      </c>
-      <c r="W30" t="n">
-        <v>38.6694721910785</v>
-      </c>
+        <v>0.9040886373526208</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
-        <v>2.730485302080482</v>
+        <v>1.887692968554678</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>73</v>
+        <v>3846.10009765625</v>
       </c>
       <c r="AA30" t="n">
-        <v>81</v>
+        <v>4247.7998046875</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
@@ -5049,7 +5041,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -5059,17 +5051,17 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>SHILCTECH</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ARIHANTCAP.NS</t>
+          <t>SHILCTECH.NS</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>Arihant Capital Markets Limited</t>
+          <t>Shilchar Technologies Limited</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr"/>
@@ -5094,116 +5086,116 @@
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP30" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2235758331127167</v>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>Positive momentum | Volume is above average | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS30" t="n">
         <v>291</v>
       </c>
       <c r="AT30" t="n">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>43.36000061035156</v>
+        <v>71</v>
       </c>
       <c r="B31" t="n">
-        <v>43.83000183105469</v>
+        <v>72.69999694824219</v>
       </c>
       <c r="C31" t="n">
-        <v>42.45999908447266</v>
+        <v>61.36999893188477</v>
       </c>
       <c r="D31" t="n">
-        <v>43.65999984741211</v>
+        <v>62.59000015258789</v>
       </c>
       <c r="E31" t="n">
-        <v>3568740</v>
+        <v>560099</v>
       </c>
       <c r="F31" t="n">
-        <v>43.86000061035156</v>
+        <v>67.83999633789062</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4559980851715939</v>
+        <v>-7.738791964483727</v>
       </c>
       <c r="H31" t="n">
-        <v>43.40800037384033</v>
+        <v>58.40999946594238</v>
       </c>
       <c r="I31" t="n">
-        <v>43.35360031127929</v>
+        <v>56.52099975585938</v>
       </c>
       <c r="J31" t="n">
-        <v>44.25790016174317</v>
+        <v>57.95149997711182</v>
       </c>
       <c r="K31" t="n">
-        <v>42.34000011444092</v>
+        <v>63.315149974823</v>
       </c>
       <c r="L31" t="n">
-        <v>44.53692680048745</v>
+        <v>59.75990263961244</v>
       </c>
       <c r="M31" t="n">
-        <v>44.12486400386921</v>
+        <v>58.56840111765532</v>
       </c>
       <c r="N31" t="n">
-        <v>43.79645011516082</v>
+        <v>57.71422464653458</v>
       </c>
       <c r="O31" t="n">
-        <v>61.90769181652171</v>
+        <v>61.77146293448224</v>
       </c>
       <c r="P31" t="n">
-        <v>1.961429050990513</v>
+        <v>3.232857022966658</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.49250814898199</v>
+        <v>5.165133431994391</v>
       </c>
       <c r="R31" t="n">
-        <v>13228506</v>
+        <v>63036.8</v>
       </c>
       <c r="S31" t="n">
-        <v>0.2697764963027571</v>
+        <v>8.885270191380272</v>
       </c>
       <c r="T31" t="n">
-        <v>53.75</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="U31" t="n">
-        <v>33.0099983215332</v>
+        <v>46.15000152587891</v>
       </c>
       <c r="V31" t="n">
-        <v>-18.77209330714026</v>
+        <v>-31.8933633151653</v>
       </c>
       <c r="W31" t="n">
-        <v>32.26295688398039</v>
+        <v>35.62296442718458</v>
       </c>
       <c r="X31" t="n">
-        <v>3.117618633451486</v>
+        <v>-1.145302226281487</v>
       </c>
       <c r="Y31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>39.29999923706055</v>
+        <v>55</v>
       </c>
       <c r="AA31" t="n">
-        <v>49.40000152587891</v>
+        <v>69.98999786376953</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Strong Uptrend</t>
+          <t>Downtrend</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5213,17 +5205,17 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>NSLNISP</t>
+          <t>SSDL</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>NSLNISP.NS</t>
+          <t>SSDL.NS</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>NMDC Steel Limited</t>
+          <t>Saraswati Saree Depot Limited</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr"/>
@@ -5248,103 +5240,111 @@
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.31651396214001</v>
+        <v>0.9749667407659449</v>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>Strong price trend | RSI supports positive momentum | Price is above 200 DMA</t>
+          <t>Price trend is weak | Strong positive momentum | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS31" t="n">
         <v>291</v>
       </c>
       <c r="AT31" t="n">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4158</v>
+        <v>209.8999938964844</v>
       </c>
       <c r="B32" t="n">
-        <v>4189</v>
+        <v>225.7599945068359</v>
       </c>
       <c r="C32" t="n">
-        <v>4084</v>
+        <v>200</v>
       </c>
       <c r="D32" t="n">
-        <v>4174.39990234375</v>
+        <v>221.1499938964844</v>
       </c>
       <c r="E32" t="n">
-        <v>17556</v>
+        <v>431750</v>
       </c>
       <c r="F32" t="n">
-        <v>4158.60009765625</v>
+        <v>210.1600036621094</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3799308497204335</v>
+        <v>5.22934432949691</v>
       </c>
       <c r="H32" t="n">
-        <v>4018.929992675781</v>
+        <v>207.3924995422363</v>
       </c>
       <c r="I32" t="n">
-        <v>4247.118017578125</v>
+        <v>220.6941989135742</v>
       </c>
       <c r="J32" t="n">
-        <v>4293.671003417969</v>
+        <v>230.0062995910644</v>
       </c>
       <c r="K32" t="n">
-        <v>4097.059989013672</v>
+        <v>234.9700498199463</v>
       </c>
       <c r="L32" t="n">
-        <v>4117.276088764583</v>
+        <v>211.102954481969</v>
       </c>
       <c r="M32" t="n">
-        <v>4109.577045023469</v>
+        <v>210.6562489849827</v>
       </c>
       <c r="N32" t="n">
-        <v>4186.058586926075</v>
+        <v>217.4850292722071</v>
       </c>
       <c r="O32" t="n">
-        <v>68.60669434597848</v>
+        <v>70.55051367402692</v>
       </c>
       <c r="P32" t="n">
-        <v>115.6857038225446</v>
+        <v>9.67499760219029</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.771313399025138</v>
+        <v>4.374857729690443</v>
       </c>
       <c r="R32" t="n">
-        <v>19418.45</v>
+        <v>153400.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0.9040886373526208</v>
-      </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+        <v>2.814531653458305</v>
+      </c>
+      <c r="T32" t="n">
+        <v>314.7000122070312</v>
+      </c>
+      <c r="U32" t="n">
+        <v>186</v>
+      </c>
+      <c r="V32" t="n">
+        <v>-29.7267285293282</v>
+      </c>
+      <c r="W32" t="n">
+        <v>18.89784618090558</v>
+      </c>
       <c r="X32" t="n">
-        <v>1.887692968554678</v>
+        <v>-5.881624459820307</v>
       </c>
       <c r="Y32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3846.10009765625</v>
+        <v>197.1300048828125</v>
       </c>
       <c r="AA32" t="n">
-        <v>4247.7998046875</v>
+        <v>219.7899932861328</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Sideways</t>
+          <t>Downtrend</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5354,22 +5354,22 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>SHILCTECH</t>
+          <t>ALLTIME</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>SHILCTECH.NS</t>
+          <t>ALLTIME.NS</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Shilchar Technologies Limited</t>
+          <t>All Time Plastics Limited</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr"/>
@@ -5386,115 +5386,115 @@
       </c>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP32" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.2235758331127167</v>
+        <v>-0.056619535070456</v>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>Strong positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is below 200 DMA</t>
         </is>
       </c>
       <c r="AS32" t="n">
-        <v>291</v>
+        <v>143</v>
       </c>
       <c r="AT32" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>71</v>
+        <v>28.59000015258789</v>
       </c>
       <c r="B33" t="n">
-        <v>72.69999694824219</v>
+        <v>32.38999938964844</v>
       </c>
       <c r="C33" t="n">
-        <v>61.36999893188477</v>
+        <v>28.43000030517578</v>
       </c>
       <c r="D33" t="n">
-        <v>62.59000015258789</v>
+        <v>31.89999961853027</v>
       </c>
       <c r="E33" t="n">
-        <v>560099</v>
+        <v>1039887</v>
       </c>
       <c r="F33" t="n">
-        <v>67.83999633789062</v>
+        <v>28.61000061035156</v>
       </c>
       <c r="G33" t="n">
-        <v>-7.738791964483727</v>
+        <v>11.49947199577597</v>
       </c>
       <c r="H33" t="n">
-        <v>58.40999946594238</v>
+        <v>29.5210000038147</v>
       </c>
       <c r="I33" t="n">
-        <v>56.52099975585938</v>
+        <v>29.81320007324219</v>
       </c>
       <c r="J33" t="n">
-        <v>57.95149997711182</v>
+        <v>30.95860004425049</v>
       </c>
       <c r="K33" t="n">
-        <v>63.315149974823</v>
+        <v>33.4475001335144</v>
       </c>
       <c r="L33" t="n">
-        <v>59.75990263961244</v>
+        <v>29.88815893587988</v>
       </c>
       <c r="M33" t="n">
-        <v>58.56840111765532</v>
+        <v>29.75932317140746</v>
       </c>
       <c r="N33" t="n">
-        <v>57.71422464653458</v>
+        <v>30.01706050052726</v>
       </c>
       <c r="O33" t="n">
-        <v>61.77146293448224</v>
+        <v>74.39799411549839</v>
       </c>
       <c r="P33" t="n">
-        <v>3.232857022966658</v>
+        <v>1.074999945504325</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.165133431994391</v>
+        <v>3.369905825578356</v>
       </c>
       <c r="R33" t="n">
-        <v>63036.8</v>
+        <v>213049.95</v>
       </c>
       <c r="S33" t="n">
-        <v>8.885270191380272</v>
+        <v>4.880953973469602</v>
       </c>
       <c r="T33" t="n">
-        <v>91.90000152587891</v>
+        <v>55.90000152587891</v>
       </c>
       <c r="U33" t="n">
-        <v>46.15000152587891</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="V33" t="n">
-        <v>-31.8933633151653</v>
+        <v>-42.93381261579722</v>
       </c>
       <c r="W33" t="n">
-        <v>35.62296442718458</v>
+        <v>25.64001727206019</v>
       </c>
       <c r="X33" t="n">
-        <v>-1.145302226281487</v>
+        <v>-4.626655232250179</v>
       </c>
       <c r="Y33" t="b">
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>55</v>
+        <v>27.60000038146973</v>
       </c>
       <c r="AA33" t="n">
-        <v>69.98999786376953</v>
+        <v>31.29999923706055</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -5508,22 +5508,22 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Confirmed Breakout</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>SSDL</t>
+          <t>TRACXN</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>SSDL.NS</t>
+          <t>TRACXN.NS</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Limited</t>
+          <t>Tracxn Technologies Limited</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr"/>
@@ -5540,119 +5540,119 @@
       </c>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Strong Breakout Watch</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="AP33" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.9749667407659449</v>
+        <v>-0.1395349971922049</v>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>Price trend is weak | Strong positive momentum | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA | Price is near 200 DMA</t>
+          <t>Price trend is weak | Strong positive momentum | Confirmed price breakout | Volume is more than 2x average | RSI indicates overbought conditions | Price is below 200 DMA</t>
         </is>
       </c>
       <c r="AS33" t="n">
-        <v>291</v>
+        <v>143</v>
       </c>
       <c r="AT33" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>140.8899993896484</v>
+        <v>372</v>
       </c>
       <c r="B34" t="n">
-        <v>140.8899993896484</v>
+        <v>390.8500061035156</v>
       </c>
       <c r="C34" t="n">
-        <v>137.8099975585938</v>
+        <v>372</v>
       </c>
       <c r="D34" t="n">
-        <v>139.4799957275391</v>
+        <v>388</v>
       </c>
       <c r="E34" t="n">
-        <v>78890</v>
+        <v>16707001</v>
       </c>
       <c r="F34" t="n">
-        <v>142.5700073242188</v>
+        <v>372</v>
       </c>
       <c r="G34" t="n">
-        <v>-2.167364409018147</v>
+        <v>4.3010752688172</v>
       </c>
       <c r="H34" t="n">
-        <v>136.4795013427734</v>
+        <v>377.3125</v>
       </c>
       <c r="I34" t="n">
-        <v>138.0780014038086</v>
+        <v>385.8669989013672</v>
       </c>
       <c r="J34" t="n">
-        <v>137.8492004394531</v>
+        <v>400.2744992065429</v>
       </c>
       <c r="K34" t="n">
-        <v>133.789100151062</v>
+        <v>415.5699993896484</v>
       </c>
       <c r="L34" t="n">
-        <v>138.0966370212621</v>
+        <v>377.9347474545086</v>
       </c>
       <c r="M34" t="n">
-        <v>137.5375874835113</v>
+        <v>378.8462663560966</v>
       </c>
       <c r="N34" t="n">
-        <v>137.5143574405532</v>
+        <v>385.9401403303</v>
       </c>
       <c r="O34" t="n">
-        <v>54.93260547511714</v>
+        <v>58.65324635017991</v>
       </c>
       <c r="P34" t="n">
-        <v>3.66785648890904</v>
+        <v>9.896429879324776</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.629664899096964</v>
+        <v>2.550626257557932</v>
       </c>
       <c r="R34" t="n">
-        <v>84209.35000000001</v>
+        <v>4552819.2</v>
       </c>
       <c r="S34" t="n">
-        <v>0.9368318363697142</v>
+        <v>3.669594654670231</v>
       </c>
       <c r="T34" t="n">
-        <v>154.25</v>
+        <v>481.5</v>
       </c>
       <c r="U34" t="n">
-        <v>114.3099975585938</v>
+        <v>337.7999877929688</v>
       </c>
       <c r="V34" t="n">
-        <v>-9.575367437575972</v>
+        <v>-19.41848390446522</v>
       </c>
       <c r="W34" t="n">
-        <v>22.01906981586935</v>
+        <v>14.86086856752579</v>
       </c>
       <c r="X34" t="n">
-        <v>4.253631700976716</v>
+        <v>-6.634261238814341</v>
       </c>
       <c r="Y34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>132.1900024414062</v>
+        <v>367.3500061035156</v>
       </c>
       <c r="AA34" t="n">
-        <v>146.5</v>
+        <v>389.3999938964844</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Uptrend</t>
+          <t>Downtrend</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5662,22 +5662,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Near Breakout</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>MUKANDLTD.NS</t>
+          <t>INDUSTOWER.NS</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Mukand Limited</t>
+          <t>Indus Towers Limited</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr"/>
@@ -5694,119 +5694,119 @@
       </c>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>Momentum Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO34" t="n">
         <v>-3</v>
       </c>
       <c r="AP34" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.9629644358952354</v>
+        <v>0.06779633463827422</v>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>Price is in an uptrend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA</t>
+          <t>Price trend is weak | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
       <c r="AS34" t="n">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="AT34" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>62.70000076293945</v>
+        <v>1028.199951171875</v>
       </c>
       <c r="B35" t="n">
-        <v>62.70000076293945</v>
+        <v>1041.5</v>
       </c>
       <c r="C35" t="n">
-        <v>59.59000015258789</v>
+        <v>1022.700012207031</v>
       </c>
       <c r="D35" t="n">
-        <v>61.47000122070312</v>
+        <v>1037.699951171875</v>
       </c>
       <c r="E35" t="n">
-        <v>162</v>
+        <v>2506618</v>
       </c>
       <c r="F35" t="n">
-        <v>60.38000106811523</v>
+        <v>1038.599975585938</v>
       </c>
       <c r="G35" t="n">
-        <v>1.805233741811718</v>
+        <v>-0.08665746535905239</v>
       </c>
       <c r="H35" t="n">
-        <v>61.17050018310547</v>
+        <v>1009.089996337891</v>
       </c>
       <c r="I35" t="n">
-        <v>61.22540000915527</v>
+        <v>1058.046002197266</v>
       </c>
       <c r="J35" t="n">
-        <v>62.4934001159668</v>
+        <v>1045.614000244141</v>
       </c>
       <c r="K35" t="n">
-        <v>59.49725004196167</v>
+        <v>1039.089999084473</v>
       </c>
       <c r="L35" t="n">
-        <v>61.23399550024929</v>
+        <v>1018.879506387137</v>
       </c>
       <c r="M35" t="n">
-        <v>61.29115784364586</v>
+        <v>1020.905804428483</v>
       </c>
       <c r="N35" t="n">
-        <v>61.38565324002825</v>
+        <v>1037.977010884295</v>
       </c>
       <c r="O35" t="n">
-        <v>55.38674524381264</v>
+        <v>59.57337392010565</v>
       </c>
       <c r="P35" t="n">
-        <v>2.781428745814732</v>
+        <v>24.34998866489955</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.524855523962387</v>
+        <v>2.346534625678752</v>
       </c>
       <c r="R35" t="n">
-        <v>1367.95</v>
+        <v>2024858.4</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1184253810446288</v>
+        <v>1.237922612267603</v>
       </c>
       <c r="T35" t="n">
-        <v>77.01000213623047</v>
+        <v>1221.900024414062</v>
       </c>
       <c r="U35" t="n">
-        <v>43.0099983215332</v>
+        <v>903</v>
       </c>
       <c r="V35" t="n">
-        <v>-20.17919813589555</v>
+        <v>-15.07488907126562</v>
       </c>
       <c r="W35" t="n">
-        <v>42.92025952004703</v>
+        <v>14.91693811427187</v>
       </c>
       <c r="X35" t="n">
-        <v>3.315701443932502</v>
+        <v>-0.1337755068206331</v>
       </c>
       <c r="Y35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>59</v>
+        <v>980.2999877929688</v>
       </c>
       <c r="AA35" t="n">
-        <v>63.4900016784668</v>
+        <v>1042.099975585938</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Uptrend</t>
+          <t>Downtrend</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5816,22 +5816,22 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>No Breakout</t>
+          <t>Near Breakout</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>SHIVAMILLS</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>SHIVAMILLS.NS</t>
+          <t>MAXHEALTH.NS</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>Shiva Mills Limited</t>
+          <t>Max Healthcare Institute Limited</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr"/>
@@ -5848,119 +5848,119 @@
       </c>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>Momentum Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO35" t="n">
         <v>-3</v>
       </c>
       <c r="AP35" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.8178135463385102</v>
+        <v>0.07665552650299168</v>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>Price is in an uptrend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA</t>
+          <t>Price trend is weak | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is below 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS35" t="n">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="AT35" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>372</v>
+        <v>140.8899993896484</v>
       </c>
       <c r="B36" t="n">
-        <v>390.8500061035156</v>
+        <v>140.8899993896484</v>
       </c>
       <c r="C36" t="n">
-        <v>372</v>
+        <v>137.8099975585938</v>
       </c>
       <c r="D36" t="n">
-        <v>388</v>
+        <v>139.4799957275391</v>
       </c>
       <c r="E36" t="n">
-        <v>16707001</v>
+        <v>78890</v>
       </c>
       <c r="F36" t="n">
-        <v>372</v>
+        <v>142.5700073242188</v>
       </c>
       <c r="G36" t="n">
-        <v>4.3010752688172</v>
+        <v>-2.167364409018147</v>
       </c>
       <c r="H36" t="n">
-        <v>377.3125</v>
+        <v>136.4795013427734</v>
       </c>
       <c r="I36" t="n">
-        <v>385.8669989013672</v>
+        <v>138.0780014038086</v>
       </c>
       <c r="J36" t="n">
-        <v>400.2744992065429</v>
+        <v>137.8492004394531</v>
       </c>
       <c r="K36" t="n">
-        <v>415.5699993896484</v>
+        <v>133.789100151062</v>
       </c>
       <c r="L36" t="n">
-        <v>377.9347474545086</v>
+        <v>138.0966370212621</v>
       </c>
       <c r="M36" t="n">
-        <v>378.8462663560966</v>
+        <v>137.5375874835113</v>
       </c>
       <c r="N36" t="n">
-        <v>385.9401403303</v>
+        <v>137.5143574405532</v>
       </c>
       <c r="O36" t="n">
-        <v>58.65324635017991</v>
+        <v>54.93260547511714</v>
       </c>
       <c r="P36" t="n">
-        <v>9.896429879324776</v>
+        <v>3.66785648890904</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.550626257557932</v>
+        <v>2.629664899096964</v>
       </c>
       <c r="R36" t="n">
-        <v>4552819.2</v>
+        <v>84209.35000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>3.669594654670231</v>
+        <v>0.9368318363697142</v>
       </c>
       <c r="T36" t="n">
-        <v>481.5</v>
+        <v>154.25</v>
       </c>
       <c r="U36" t="n">
-        <v>337.7999877929688</v>
+        <v>114.3099975585938</v>
       </c>
       <c r="V36" t="n">
-        <v>-19.41848390446522</v>
+        <v>-9.575367437575972</v>
       </c>
       <c r="W36" t="n">
-        <v>14.86086856752579</v>
+        <v>22.01906981586935</v>
       </c>
       <c r="X36" t="n">
-        <v>-6.634261238814341</v>
+        <v>4.253631700976716</v>
       </c>
       <c r="Y36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="n">
-        <v>367.3500061035156</v>
+        <v>132.1900024414062</v>
       </c>
       <c r="AA36" t="n">
-        <v>389.3999938964844</v>
+        <v>146.5</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Downtrend</t>
+          <t>Uptrend</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5970,22 +5970,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Near Breakout</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>MUKANDLTD</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>INDUSTOWER.NS</t>
+          <t>MUKANDLTD.NS</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Indus Towers Limited</t>
+          <t>Mukand Limited</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr"/>
@@ -6002,119 +6002,119 @@
       </c>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Momentum Watch</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="AP36" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.06779633463827422</v>
+        <v>0.9629644358952354</v>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>Price trend is weak | Positive momentum | Price is close to resistance | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
+          <t>Price is in an uptrend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS36" t="n">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="AT36" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1028.199951171875</v>
+        <v>62.70000076293945</v>
       </c>
       <c r="B37" t="n">
-        <v>1041.5</v>
+        <v>62.70000076293945</v>
       </c>
       <c r="C37" t="n">
-        <v>1022.700012207031</v>
+        <v>59.59000015258789</v>
       </c>
       <c r="D37" t="n">
-        <v>1037.699951171875</v>
+        <v>61.47000122070312</v>
       </c>
       <c r="E37" t="n">
-        <v>2506618</v>
+        <v>162</v>
       </c>
       <c r="F37" t="n">
-        <v>1038.599975585938</v>
+        <v>60.38000106811523</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.08665746535905239</v>
+        <v>1.805233741811718</v>
       </c>
       <c r="H37" t="n">
-        <v>1009.089996337891</v>
+        <v>61.17050018310547</v>
       </c>
       <c r="I37" t="n">
-        <v>1058.046002197266</v>
+        <v>61.22540000915527</v>
       </c>
       <c r="J37" t="n">
-        <v>1045.614000244141</v>
+        <v>62.4934001159668</v>
       </c>
       <c r="K37" t="n">
-        <v>1039.089999084473</v>
+        <v>59.49725004196167</v>
       </c>
       <c r="L37" t="n">
-        <v>1018.879506387137</v>
+        <v>61.23399550024929</v>
       </c>
       <c r="M37" t="n">
-        <v>1020.905804428483</v>
+        <v>61.29115784364586</v>
       </c>
       <c r="N37" t="n">
-        <v>1037.977010884295</v>
+        <v>61.38565324002825</v>
       </c>
       <c r="O37" t="n">
-        <v>59.57337392010565</v>
+        <v>55.38674524381264</v>
       </c>
       <c r="P37" t="n">
-        <v>24.34998866489955</v>
+        <v>2.781428745814732</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.346534625678752</v>
+        <v>4.524855523962387</v>
       </c>
       <c r="R37" t="n">
-        <v>2024858.4</v>
+        <v>1367.95</v>
       </c>
       <c r="S37" t="n">
-        <v>1.237922612267603</v>
+        <v>0.1184253810446288</v>
       </c>
       <c r="T37" t="n">
-        <v>1221.900024414062</v>
+        <v>77.01000213623047</v>
       </c>
       <c r="U37" t="n">
-        <v>903</v>
+        <v>43.0099983215332</v>
       </c>
       <c r="V37" t="n">
-        <v>-15.07488907126562</v>
+        <v>-20.17919813589555</v>
       </c>
       <c r="W37" t="n">
-        <v>14.91693811427187</v>
+        <v>42.92025952004703</v>
       </c>
       <c r="X37" t="n">
-        <v>-0.1337755068206331</v>
+        <v>3.315701443932502</v>
       </c>
       <c r="Y37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="n">
-        <v>980.2999877929688</v>
+        <v>59</v>
       </c>
       <c r="AA37" t="n">
-        <v>1042.099975585938</v>
+        <v>63.4900016784668</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Downtrend</t>
+          <t>Uptrend</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6124,22 +6124,22 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Near Breakout</t>
+          <t>No Breakout</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>SHIVAMILLS</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>MAXHEALTH.NS</t>
+          <t>SHIVAMILLS.NS</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Limited</t>
+          <t>Shiva Mills Limited</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr"/>
@@ -6156,32 +6156,32 @@
       </c>
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Momentum Watch</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="AP37" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.07665552650299168</v>
+        <v>0.8178135463385102</v>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>Price trend is weak | Positive momentum | Price is close to resistance | Volume is above average | RSI supports positive momentum | Price is below 200 DMA | Price is near 200 DMA</t>
+          <t>Price is in an uptrend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS37" t="n">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="AT37" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="38">
@@ -6318,10 +6318,10 @@
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP38" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.4978097238407234</v>
@@ -6335,7 +6335,7 @@
         <v>419</v>
       </c>
       <c r="AT38" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP39" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.6154451577970297</v>
@@ -6489,7 +6489,7 @@
         <v>419</v>
       </c>
       <c r="AT39" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40">
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP40" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.7221311280625461</v>
@@ -6643,7 +6643,7 @@
         <v>419</v>
       </c>
       <c r="AT40" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41">
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP41" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.413560809618138</v>
@@ -6797,7 +6797,7 @@
         <v>419</v>
       </c>
       <c r="AT41" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42">
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP42" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.2509652115374494</v>
@@ -6951,7 +6951,7 @@
         <v>419</v>
       </c>
       <c r="AT42" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="43">
@@ -7088,10 +7088,10 @@
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP43" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.6884164083449024</v>
@@ -7105,7 +7105,7 @@
         <v>419</v>
       </c>
       <c r="AT43" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="44">
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP44" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.6676386914811033</v>
@@ -7259,7 +7259,7 @@
         <v>419</v>
       </c>
       <c r="AT44" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="45">
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP45" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.050227139711825</v>
@@ -7413,7 +7413,7 @@
         <v>419</v>
       </c>
       <c r="AT45" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46">
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP46" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.1845141672926037</v>
@@ -7567,7 +7567,7 @@
         <v>419</v>
       </c>
       <c r="AT46" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="47">
@@ -7704,10 +7704,10 @@
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP47" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.4437082278186812</v>
@@ -7721,7 +7721,7 @@
         <v>419</v>
       </c>
       <c r="AT47" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48">
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP48" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.3361839242818236</v>
@@ -7875,99 +7875,99 @@
         <v>419</v>
       </c>
       <c r="AT48" t="n">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>547</v>
+        <v>16.6200008392334</v>
       </c>
       <c r="B49" t="n">
-        <v>549.75</v>
+        <v>17.36000061035156</v>
       </c>
       <c r="C49" t="n">
-        <v>533</v>
+        <v>16.5</v>
       </c>
       <c r="D49" t="n">
-        <v>538.4500122070312</v>
+        <v>17.1299991607666</v>
       </c>
       <c r="E49" t="n">
-        <v>90810</v>
+        <v>109228</v>
       </c>
       <c r="F49" t="n">
-        <v>551.9500122070312</v>
+        <v>17.04000091552734</v>
       </c>
       <c r="G49" t="n">
-        <v>-2.445873666352283</v>
+        <v>0.5281586878158384</v>
       </c>
       <c r="H49" t="n">
-        <v>536.4300018310547</v>
+        <v>15.47199993133545</v>
       </c>
       <c r="I49" t="n">
-        <v>538.1160046386718</v>
+        <v>15.37719997406006</v>
       </c>
       <c r="J49" t="n">
-        <v>546.7600045776367</v>
+        <v>15.99489998817444</v>
       </c>
       <c r="K49" t="n">
-        <v>533.2492529296875</v>
+        <v>16.38345003128052</v>
       </c>
       <c r="L49" t="n">
-        <v>540.9751289925978</v>
+        <v>16.32090213802311</v>
       </c>
       <c r="M49" t="n">
-        <v>538.2562352936815</v>
+        <v>15.7682828995783</v>
       </c>
       <c r="N49" t="n">
-        <v>537.9562395903937</v>
+        <v>15.60600392191063</v>
       </c>
       <c r="O49" t="n">
-        <v>52.21483822650723</v>
+        <v>72.24577337084725</v>
       </c>
       <c r="P49" t="n">
-        <v>17.6999991280692</v>
+        <v>0.8600001335144043</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.287213060970948</v>
+        <v>5.020433016039433</v>
       </c>
       <c r="R49" t="n">
-        <v>139203.2</v>
+        <v>117409.75</v>
       </c>
       <c r="S49" t="n">
-        <v>0.6523556929725753</v>
+        <v>0.9303145607583697</v>
       </c>
       <c r="T49" t="n">
-        <v>667.5499877929688</v>
+        <v>27.48999977111816</v>
       </c>
       <c r="U49" t="n">
-        <v>416</v>
+        <v>12.63000011444092</v>
       </c>
       <c r="V49" t="n">
-        <v>-19.33937202407321</v>
+        <v>-37.68643396365574</v>
       </c>
       <c r="W49" t="n">
-        <v>29.43509908822867</v>
+        <v>35.6294458080049</v>
       </c>
       <c r="X49" t="n">
-        <v>0.9752961206735191</v>
+        <v>4.556727234256009</v>
       </c>
       <c r="Y49" t="b">
         <v>1</v>
       </c>
       <c r="Z49" t="n">
-        <v>499.0499877929688</v>
+        <v>14.18000030517578</v>
       </c>
       <c r="AA49" t="n">
-        <v>572.5999755859375</v>
+        <v>18.04999923706055</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Uptrend</t>
+          <t>Sideways</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>CARRARO</t>
+          <t>AIRAN</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>CARRARO.NS</t>
+          <t>AIRAN.NS</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Carraro India Limited</t>
+          <t>Airan Limited</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr"/>
@@ -8004,124 +8004,124 @@
       </c>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>Momentum Watch</t>
+          <t>200 DMA Recovery Watch</t>
         </is>
       </c>
       <c r="AO49" t="n">
         <v>-3</v>
       </c>
       <c r="AP49" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.8667498024878781</v>
+        <v>0.3118645536252893</v>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>Price is in an uptrend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
+          <t>Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS49" t="n">
-        <v>445</v>
+        <v>493</v>
       </c>
       <c r="AT49" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>16.6200008392334</v>
+        <v>10990</v>
       </c>
       <c r="B50" t="n">
-        <v>17.36000061035156</v>
+        <v>11146</v>
       </c>
       <c r="C50" t="n">
-        <v>16.5</v>
+        <v>10922</v>
       </c>
       <c r="D50" t="n">
-        <v>17.1299991607666</v>
+        <v>11134</v>
       </c>
       <c r="E50" t="n">
-        <v>109228</v>
+        <v>49910</v>
       </c>
       <c r="F50" t="n">
-        <v>17.04000091552734</v>
+        <v>10992</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5281586878158384</v>
+        <v>1.291848617176128</v>
       </c>
       <c r="H50" t="n">
-        <v>15.47199993133545</v>
+        <v>11248.85</v>
       </c>
       <c r="I50" t="n">
-        <v>15.37719997406006</v>
+        <v>11057.86</v>
       </c>
       <c r="J50" t="n">
-        <v>15.99489998817444</v>
+        <v>10740.145</v>
       </c>
       <c r="K50" t="n">
-        <v>16.38345003128052</v>
+        <v>10681.365</v>
       </c>
       <c r="L50" t="n">
-        <v>16.32090213802311</v>
+        <v>11126.47640847664</v>
       </c>
       <c r="M50" t="n">
-        <v>15.7682828995783</v>
+        <v>11187.22142649512</v>
       </c>
       <c r="N50" t="n">
-        <v>15.60600392191063</v>
+        <v>11067.57002171489</v>
       </c>
       <c r="O50" t="n">
-        <v>72.24577337084725</v>
+        <v>50.33460803059274</v>
       </c>
       <c r="P50" t="n">
-        <v>0.8600001335144043</v>
+        <v>255.6428571428571</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.020433016039433</v>
+        <v>2.296055839256845</v>
       </c>
       <c r="R50" t="n">
-        <v>117409.75</v>
+        <v>46840.35</v>
       </c>
       <c r="S50" t="n">
-        <v>0.9303145607583697</v>
+        <v>1.065534309628344</v>
       </c>
       <c r="T50" t="n">
-        <v>27.48999977111816</v>
+        <v>13880</v>
       </c>
       <c r="U50" t="n">
-        <v>12.63000011444092</v>
+        <v>8588</v>
       </c>
       <c r="V50" t="n">
-        <v>-37.68643396365574</v>
+        <v>-19.78386167146974</v>
       </c>
       <c r="W50" t="n">
-        <v>35.6294458080049</v>
+        <v>29.64601769911505</v>
       </c>
       <c r="X50" t="n">
-        <v>4.556727234256009</v>
+        <v>4.237613825573793</v>
       </c>
       <c r="Y50" t="b">
         <v>1</v>
       </c>
       <c r="Z50" t="n">
-        <v>14.18000030517578</v>
+        <v>10811</v>
       </c>
       <c r="AA50" t="n">
-        <v>18.04999923706055</v>
+        <v>11644</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Sideways</t>
+          <t>Uptrend</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -8131,17 +8131,17 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>AIRAN.NS</t>
+          <t>BAJAJHLDNG.NS</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>Airan Limited</t>
+          <t>Bajaj Holdings &amp; Investment Limited</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr"/>
@@ -8166,116 +8166,116 @@
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP50" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.3118645536252893</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA</t>
+          <t>Price is in an uptrend | RSI supports positive momentum | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS50" t="n">
         <v>493</v>
       </c>
       <c r="AT50" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10990</v>
+        <v>64.69999694824219</v>
       </c>
       <c r="B51" t="n">
-        <v>11146</v>
+        <v>69.72000122070312</v>
       </c>
       <c r="C51" t="n">
-        <v>10922</v>
+        <v>63.11999893188477</v>
       </c>
       <c r="D51" t="n">
-        <v>11134</v>
+        <v>65.69000244140625</v>
       </c>
       <c r="E51" t="n">
-        <v>49910</v>
+        <v>101530</v>
       </c>
       <c r="F51" t="n">
-        <v>10992</v>
+        <v>63.84999847412109</v>
       </c>
       <c r="G51" t="n">
-        <v>1.291848617176128</v>
+        <v>2.881760393511867</v>
       </c>
       <c r="H51" t="n">
-        <v>11248.85</v>
+        <v>63.35900001525879</v>
       </c>
       <c r="I51" t="n">
-        <v>11057.86</v>
+        <v>64.80680007934571</v>
       </c>
       <c r="J51" t="n">
-        <v>10740.145</v>
+        <v>63.20880035400391</v>
       </c>
       <c r="K51" t="n">
-        <v>10681.365</v>
+        <v>68.05685005187988</v>
       </c>
       <c r="L51" t="n">
-        <v>11126.47640847664</v>
+        <v>64.49644339380183</v>
       </c>
       <c r="M51" t="n">
-        <v>11187.22142649512</v>
+        <v>64.01161009952359</v>
       </c>
       <c r="N51" t="n">
-        <v>11067.57002171489</v>
+        <v>64.13507690222818</v>
       </c>
       <c r="O51" t="n">
-        <v>50.33460803059274</v>
+        <v>62.86749038388876</v>
       </c>
       <c r="P51" t="n">
-        <v>255.6428571428571</v>
+        <v>3.624999727521624</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.296055839256845</v>
+        <v>5.518343115841757</v>
       </c>
       <c r="R51" t="n">
-        <v>46840.35</v>
+        <v>29004.7</v>
       </c>
       <c r="S51" t="n">
-        <v>1.065534309628344</v>
+        <v>3.500467165666254</v>
       </c>
       <c r="T51" t="n">
-        <v>13880</v>
+        <v>163.8999938964844</v>
       </c>
       <c r="U51" t="n">
-        <v>8588</v>
+        <v>36.29999923706055</v>
       </c>
       <c r="V51" t="n">
-        <v>-19.78386167146974</v>
+        <v>-59.92068036140709</v>
       </c>
       <c r="W51" t="n">
-        <v>29.64601769911505</v>
+        <v>80.96419785689673</v>
       </c>
       <c r="X51" t="n">
-        <v>4.237613825573793</v>
+        <v>-3.477750746132644</v>
       </c>
       <c r="Y51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>10811</v>
+        <v>58.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>11644</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Uptrend</t>
+          <t>Downtrend</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BROOKS</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG.NS</t>
+          <t>BROOKS.NS</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Limited</t>
+          <t>Brooks Laboratories Limited</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr"/>
@@ -8320,107 +8320,107 @@
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.578947368421053</v>
+        <v>0.7941581565521515</v>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>Price is in an uptrend | RSI supports positive momentum | Price is above 200 DMA</t>
+          <t>Price trend is weak | Strong positive momentum | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
         </is>
       </c>
       <c r="AS51" t="n">
         <v>493</v>
       </c>
       <c r="AT51" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>64.69999694824219</v>
+        <v>89</v>
       </c>
       <c r="B52" t="n">
-        <v>69.72000122070312</v>
+        <v>89</v>
       </c>
       <c r="C52" t="n">
-        <v>63.11999893188477</v>
+        <v>86</v>
       </c>
       <c r="D52" t="n">
-        <v>65.69000244140625</v>
+        <v>88.94999694824219</v>
       </c>
       <c r="E52" t="n">
-        <v>101530</v>
+        <v>18027</v>
       </c>
       <c r="F52" t="n">
-        <v>63.84999847412109</v>
+        <v>89.23000335693359</v>
       </c>
       <c r="G52" t="n">
-        <v>2.881760393511867</v>
+        <v>-0.3138029789950147</v>
       </c>
       <c r="H52" t="n">
-        <v>63.35900001525879</v>
+        <v>86.2390007019043</v>
       </c>
       <c r="I52" t="n">
-        <v>64.80680007934571</v>
+        <v>87.59259994506836</v>
       </c>
       <c r="J52" t="n">
-        <v>63.20880035400391</v>
+        <v>87.29060005187988</v>
       </c>
       <c r="K52" t="n">
-        <v>68.05685005187988</v>
+        <v>89.0596000289917</v>
       </c>
       <c r="L52" t="n">
-        <v>64.49644339380183</v>
+        <v>89.02055013821949</v>
       </c>
       <c r="M52" t="n">
-        <v>64.01161009952359</v>
+        <v>87.75072076258729</v>
       </c>
       <c r="N52" t="n">
-        <v>64.13507690222818</v>
+        <v>87.39788786355565</v>
       </c>
       <c r="O52" t="n">
-        <v>62.86749038388876</v>
+        <v>67.15209730066056</v>
       </c>
       <c r="P52" t="n">
-        <v>3.624999727521624</v>
+        <v>3.638571602957589</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.518343115841757</v>
+        <v>4.090580919384162</v>
       </c>
       <c r="R52" t="n">
-        <v>29004.7</v>
+        <v>9592.85</v>
       </c>
       <c r="S52" t="n">
-        <v>3.500467165666254</v>
+        <v>1.879212121528013</v>
       </c>
       <c r="T52" t="n">
-        <v>163.8999938964844</v>
+        <v>116.9000015258789</v>
       </c>
       <c r="U52" t="n">
-        <v>36.29999923706055</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="V52" t="n">
-        <v>-59.92068036140709</v>
+        <v>-23.90932781249729</v>
       </c>
       <c r="W52" t="n">
-        <v>80.96419785689673</v>
+        <v>47.51243461637272</v>
       </c>
       <c r="X52" t="n">
-        <v>-3.477750746132644</v>
+        <v>-0.1230671154079168</v>
       </c>
       <c r="Y52" t="b">
         <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>58.5</v>
+        <v>80.09999847412109</v>
       </c>
       <c r="AA52" t="n">
-        <v>71.40000152587891</v>
+        <v>94.98999786376953</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8439,17 +8439,17 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>EMMBI</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>BROOKS.NS</t>
+          <t>EMMBI.NS</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>Brooks Laboratories Limited</t>
+          <t>Emmbi Industries Limited</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr"/>
@@ -8474,116 +8474,116 @@
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.7941581565521515</v>
+        <v>0.6824860968269472</v>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>Price trend is weak | Strong positive momentum | Volume is more than 2x average | RSI supports positive momentum | Price is below 200 DMA</t>
+          <t>Price trend is weak | Positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is below 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS52" t="n">
         <v>493</v>
       </c>
       <c r="AT52" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="B53" t="n">
-        <v>89</v>
+        <v>178.3000030517578</v>
       </c>
       <c r="C53" t="n">
-        <v>86</v>
+        <v>171.0099945068359</v>
       </c>
       <c r="D53" t="n">
-        <v>88.94999694824219</v>
+        <v>175.5399932861328</v>
       </c>
       <c r="E53" t="n">
-        <v>18027</v>
+        <v>471310</v>
       </c>
       <c r="F53" t="n">
-        <v>89.23000335693359</v>
+        <v>177.3399963378906</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.3138029789950147</v>
+        <v>-1.015001177922781</v>
       </c>
       <c r="H53" t="n">
-        <v>86.2390007019043</v>
+        <v>165.1974990844727</v>
       </c>
       <c r="I53" t="n">
-        <v>87.59259994506836</v>
+        <v>165.6407989501953</v>
       </c>
       <c r="J53" t="n">
-        <v>87.29060005187988</v>
+        <v>163.5602993774414</v>
       </c>
       <c r="K53" t="n">
-        <v>89.0596000289917</v>
+        <v>168.5609994506836</v>
       </c>
       <c r="L53" t="n">
-        <v>89.02055013821949</v>
+        <v>173.1477389563621</v>
       </c>
       <c r="M53" t="n">
-        <v>87.75072076258729</v>
+        <v>168.6013230309602</v>
       </c>
       <c r="N53" t="n">
-        <v>87.39788786355565</v>
+        <v>165.4725127733566</v>
       </c>
       <c r="O53" t="n">
-        <v>67.15209730066056</v>
+        <v>70.98728860035408</v>
       </c>
       <c r="P53" t="n">
-        <v>3.638571602957589</v>
+        <v>5.868571690150669</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.090580919384162</v>
+        <v>3.34315364851633</v>
       </c>
       <c r="R53" t="n">
-        <v>9592.85</v>
+        <v>523597.45</v>
       </c>
       <c r="S53" t="n">
-        <v>1.879212121528013</v>
+        <v>0.9001380736288918</v>
       </c>
       <c r="T53" t="n">
-        <v>116.9000015258789</v>
+        <v>279.8999938964844</v>
       </c>
       <c r="U53" t="n">
-        <v>60.29999923706055</v>
+        <v>129.1000061035156</v>
       </c>
       <c r="V53" t="n">
-        <v>-23.90932781249729</v>
+        <v>-37.28474558271949</v>
       </c>
       <c r="W53" t="n">
-        <v>47.51243461637272</v>
+        <v>35.97210301088634</v>
       </c>
       <c r="X53" t="n">
-        <v>-0.1230671154079168</v>
+        <v>4.140337241825077</v>
       </c>
       <c r="Y53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z53" t="n">
-        <v>80.09999847412109</v>
+        <v>150.0599975585938</v>
       </c>
       <c r="AA53" t="n">
-        <v>94.98999786376953</v>
+        <v>182.5</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Downtrend</t>
+          <t>Sideways</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Strong Positive</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8593,17 +8593,17 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>EMMBI</t>
+          <t>PENIND</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>EMMBI.NS</t>
+          <t>PENIND.NS</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>Emmbi Industries Limited</t>
+          <t>Pennar Industries Limited</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr"/>
@@ -8628,116 +8628,116 @@
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP53" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.6824860968269472</v>
+        <v>0.2731557253106104</v>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>Price trend is weak | Positive momentum | Strong volume confirmation | RSI supports positive momentum | Price is below 200 DMA | Price is near 200 DMA</t>
+          <t>Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA</t>
         </is>
       </c>
       <c r="AS53" t="n">
         <v>493</v>
       </c>
       <c r="AT53" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>175</v>
+        <v>547</v>
       </c>
       <c r="B54" t="n">
-        <v>178.3000030517578</v>
+        <v>549.75</v>
       </c>
       <c r="C54" t="n">
-        <v>171.0099945068359</v>
+        <v>533</v>
       </c>
       <c r="D54" t="n">
-        <v>175.5399932861328</v>
+        <v>538.4500122070312</v>
       </c>
       <c r="E54" t="n">
-        <v>471310</v>
+        <v>90810</v>
       </c>
       <c r="F54" t="n">
-        <v>177.3399963378906</v>
+        <v>551.9500122070312</v>
       </c>
       <c r="G54" t="n">
-        <v>-1.015001177922781</v>
+        <v>-2.445873666352283</v>
       </c>
       <c r="H54" t="n">
-        <v>165.1974990844727</v>
+        <v>536.4300018310547</v>
       </c>
       <c r="I54" t="n">
-        <v>165.6407989501953</v>
+        <v>538.1160046386718</v>
       </c>
       <c r="J54" t="n">
-        <v>163.5602993774414</v>
+        <v>546.7600045776367</v>
       </c>
       <c r="K54" t="n">
-        <v>168.5609994506836</v>
+        <v>533.2492529296875</v>
       </c>
       <c r="L54" t="n">
-        <v>173.1477389563621</v>
+        <v>540.9751289925978</v>
       </c>
       <c r="M54" t="n">
-        <v>168.6013230309602</v>
+        <v>538.2562352936815</v>
       </c>
       <c r="N54" t="n">
-        <v>165.4725127733566</v>
+        <v>537.9562395903937</v>
       </c>
       <c r="O54" t="n">
-        <v>70.98728860035408</v>
+        <v>52.21483822650723</v>
       </c>
       <c r="P54" t="n">
-        <v>5.868571690150669</v>
+        <v>17.6999991280692</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.34315364851633</v>
+        <v>3.287213060970948</v>
       </c>
       <c r="R54" t="n">
-        <v>523597.45</v>
+        <v>139203.2</v>
       </c>
       <c r="S54" t="n">
-        <v>0.9001380736288918</v>
+        <v>0.6523556929725753</v>
       </c>
       <c r="T54" t="n">
-        <v>279.8999938964844</v>
+        <v>667.5499877929688</v>
       </c>
       <c r="U54" t="n">
-        <v>129.1000061035156</v>
+        <v>416</v>
       </c>
       <c r="V54" t="n">
-        <v>-37.28474558271949</v>
+        <v>-19.33937202407321</v>
       </c>
       <c r="W54" t="n">
-        <v>35.97210301088634</v>
+        <v>29.43509908822867</v>
       </c>
       <c r="X54" t="n">
-        <v>4.140337241825077</v>
+        <v>0.9752961206735191</v>
       </c>
       <c r="Y54" t="b">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>150.0599975585938</v>
+        <v>499.0499877929688</v>
       </c>
       <c r="AA54" t="n">
-        <v>182.5</v>
+        <v>572.5999755859375</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Sideways</t>
+          <t>Uptrend</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8747,17 +8747,17 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>PENIND</t>
+          <t>CARRARO</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>PENIND.NS</t>
+          <t>CARRARO.NS</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>Pennar Industries Limited</t>
+          <t>Carraro India Limited</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr"/>
@@ -8774,32 +8774,32 @@
       </c>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>200 DMA Recovery Watch</t>
+          <t>Momentum Watch</t>
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="AP54" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.2731557253106104</v>
+        <v>0.8667498024878781</v>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>Strong positive momentum | RSI indicates overbought conditions | Price is above 200 DMA</t>
+          <t>Price is in an uptrend | Positive momentum | RSI supports positive momentum | Price is above 200 DMA | Price is near 200 DMA</t>
         </is>
       </c>
       <c r="AS54" t="n">
-        <v>493</v>
+        <v>445</v>
       </c>
       <c r="AT54" t="n">
-        <v>451</v>
+        <v>464</v>
       </c>
     </row>
     <row r="55">
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP55" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.8600006103515625</v>
@@ -8953,7 +8953,7 @@
         <v>525</v>
       </c>
       <c r="AT55" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
     </row>
     <row r="56">
@@ -9090,10 +9090,10 @@
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP56" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.9326176800824333</v>
@@ -9107,7 +9107,7 @@
         <v>525</v>
       </c>
       <c r="AT56" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
     </row>
     <row r="57">
@@ -9244,10 +9244,10 @@
         </is>
       </c>
       <c r="AO57" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP57" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.8531319743889562</v>
@@ -9261,7 +9261,7 @@
         <v>525</v>
       </c>
       <c r="AT57" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
     </row>
     <row r="58">
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="AO58" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP58" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.4765101759368621</v>
@@ -9415,7 +9415,7 @@
         <v>525</v>
       </c>
       <c r="AT58" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
     </row>
     <row r="59">
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="AO59" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.4455232863183235</v>
@@ -9569,7 +9569,7 @@
         <v>525</v>
       </c>
       <c r="AT59" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
     </row>
     <row r="60">
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="AO60" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.6545963429873254</v>
@@ -9723,7 +9723,7 @@
         <v>525</v>
       </c>
       <c r="AT60" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
     </row>
     <row r="61">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="AO61" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.8903305584228456</v>
@@ -9877,7 +9877,7 @@
         <v>525</v>
       </c>
       <c r="AT61" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62">
@@ -10014,10 +10014,10 @@
         </is>
       </c>
       <c r="AO62" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP62" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.9295339667898578</v>
@@ -10031,7 +10031,7 @@
         <v>525</v>
       </c>
       <c r="AT62" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
     </row>
     <row r="63">
@@ -10168,10 +10168,10 @@
         </is>
       </c>
       <c r="AO63" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP63" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.877096353126082</v>
@@ -10185,7 +10185,7 @@
         <v>565</v>
       </c>
       <c r="AT63" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="64">
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AO64" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP64" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.219512648982592</v>
@@ -10339,7 +10339,7 @@
         <v>565</v>
       </c>
       <c r="AT64" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65">
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="AO65" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP65" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.3489745728430948</v>
@@ -10493,7 +10493,7 @@
         <v>565</v>
       </c>
       <c r="AT65" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66">
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="AO66" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP66" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.091743456395217</v>
@@ -10647,7 +10647,7 @@
         <v>565</v>
       </c>
       <c r="AT66" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="67">
@@ -10784,10 +10784,10 @@
         </is>
       </c>
       <c r="AO67" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP67" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.09489092905217267</v>
@@ -10801,7 +10801,7 @@
         <v>565</v>
       </c>
       <c r="AT67" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="68">
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="AO68" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP68" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.165493378679873</v>
@@ -10955,7 +10955,7 @@
         <v>565</v>
       </c>
       <c r="AT68" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="69">
@@ -11092,10 +11092,10 @@
         </is>
       </c>
       <c r="AO69" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP69" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.530611470360693</v>
@@ -11109,7 +11109,7 @@
         <v>603</v>
       </c>
       <c r="AT69" t="n">
-        <v>595</v>
+        <v>582</v>
       </c>
     </row>
     <row r="70">
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="AO70" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP70" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.116541861387766</v>
@@ -11263,7 +11263,7 @@
         <v>603</v>
       </c>
       <c r="AT70" t="n">
-        <v>595</v>
+        <v>582</v>
       </c>
     </row>
     <row r="71">
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="AO71" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP71" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.6920248394363497</v>
@@ -11417,7 +11417,7 @@
         <v>603</v>
       </c>
       <c r="AT71" t="n">
-        <v>595</v>
+        <v>582</v>
       </c>
     </row>
     <row r="72">
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="AO72" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP72" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.1106884911203069</v>
@@ -11571,7 +11571,7 @@
         <v>603</v>
       </c>
       <c r="AT72" t="n">
-        <v>595</v>
+        <v>582</v>
       </c>
     </row>
     <row r="73">
@@ -11708,10 +11708,10 @@
         </is>
       </c>
       <c r="AO73" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP73" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.8835628249679931</v>
@@ -11725,7 +11725,7 @@
         <v>603</v>
       </c>
       <c r="AT73" t="n">
-        <v>595</v>
+        <v>582</v>
       </c>
     </row>
     <row r="74">
@@ -11862,10 +11862,10 @@
         </is>
       </c>
       <c r="AO74" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP74" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.5679729918215961</v>
@@ -11879,7 +11879,7 @@
         <v>603</v>
       </c>
       <c r="AT74" t="n">
-        <v>595</v>
+        <v>582</v>
       </c>
     </row>
     <row r="75">
@@ -12016,10 +12016,10 @@
         </is>
       </c>
       <c r="AO75" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP75" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.7142853604176846</v>
@@ -12033,7 +12033,7 @@
         <v>617</v>
       </c>
       <c r="AT75" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="76">
@@ -12170,10 +12170,10 @@
         </is>
       </c>
       <c r="AO76" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP76" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.397522704519076</v>
@@ -12187,7 +12187,7 @@
         <v>617</v>
       </c>
       <c r="AT76" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="77">
@@ -12316,10 +12316,10 @@
         </is>
       </c>
       <c r="AO77" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP77" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.1677284647743821</v>
@@ -12333,7 +12333,7 @@
         <v>617</v>
       </c>
       <c r="AT77" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="78">
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="AO78" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP78" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.293232640616776</v>
@@ -12487,7 +12487,7 @@
         <v>617</v>
       </c>
       <c r="AT78" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="79">
@@ -12624,10 +12624,10 @@
         </is>
       </c>
       <c r="AO79" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP79" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.7804385393716303</v>
@@ -12641,7 +12641,7 @@
         <v>617</v>
       </c>
       <c r="AT79" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="80">
@@ -12778,10 +12778,10 @@
         </is>
       </c>
       <c r="AO80" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP80" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ80" t="n">
         <v>2.36787955293541</v>
@@ -12795,7 +12795,7 @@
         <v>617</v>
       </c>
       <c r="AT80" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="81">
@@ -12932,10 +12932,10 @@
         </is>
       </c>
       <c r="AO81" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP81" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.9115654073026321</v>
@@ -12949,7 +12949,7 @@
         <v>617</v>
       </c>
       <c r="AT81" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="82">
@@ -13086,10 +13086,10 @@
         </is>
       </c>
       <c r="AO82" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP82" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.24181291269823</v>
@@ -13103,7 +13103,7 @@
         <v>617</v>
       </c>
       <c r="AT82" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="83">
@@ -13240,10 +13240,10 @@
         </is>
       </c>
       <c r="AO83" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP83" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.9925044323706034</v>
@@ -13257,7 +13257,7 @@
         <v>617</v>
       </c>
       <c r="AT83" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="84">
@@ -13394,10 +13394,10 @@
         </is>
       </c>
       <c r="AO84" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP84" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ84" t="n">
         <v>2.419755906309089</v>
@@ -13411,7 +13411,7 @@
         <v>617</v>
       </c>
       <c r="AT84" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="85">
@@ -13548,10 +13548,10 @@
         </is>
       </c>
       <c r="AO85" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP85" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AQ85" t="n">
         <v>2.940297147802422</v>
@@ -13565,7 +13565,7 @@
         <v>617</v>
       </c>
       <c r="AT85" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="86">
@@ -13702,10 +13702,10 @@
         </is>
       </c>
       <c r="AO86" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP86" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.689074710766974</v>
@@ -13719,7 +13719,7 @@
         <v>638</v>
       </c>
       <c r="AT86" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="87">
@@ -13856,10 +13856,10 @@
         </is>
       </c>
       <c r="AO87" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP87" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.3235291477718682</v>
@@ -13873,7 +13873,7 @@
         <v>638</v>
       </c>
       <c r="AT87" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="88">
@@ -14010,10 +14010,10 @@
         </is>
       </c>
       <c r="AO88" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP88" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.82736018737982</v>
@@ -14027,7 +14027,7 @@
         <v>638</v>
       </c>
       <c r="AT88" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="89">
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="AO89" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP89" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.354949080957502</v>
@@ -14181,7 +14181,7 @@
         <v>638</v>
       </c>
       <c r="AT89" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="90">
@@ -14318,10 +14318,10 @@
         </is>
       </c>
       <c r="AO90" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP90" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.09475055488779831</v>
@@ -14335,7 +14335,7 @@
         <v>638</v>
       </c>
       <c r="AT90" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="91">
@@ -14472,10 +14472,10 @@
         </is>
       </c>
       <c r="AO91" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP91" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.9599997780539773</v>
@@ -14489,7 +14489,7 @@
         <v>638</v>
       </c>
       <c r="AT91" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="92">
@@ -14626,10 +14626,10 @@
         </is>
       </c>
       <c r="AO92" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP92" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.8325260848711679</v>
@@ -14643,7 +14643,7 @@
         <v>638</v>
       </c>
       <c r="AT92" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="93">
@@ -14780,10 +14780,10 @@
         </is>
       </c>
       <c r="AO93" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP93" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.1332196769067797</v>
@@ -14797,7 +14797,7 @@
         <v>638</v>
       </c>
       <c r="AT93" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="94">
@@ -14934,10 +14934,10 @@
         </is>
       </c>
       <c r="AO94" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP94" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.9230766409247999</v>
@@ -14951,7 +14951,7 @@
         <v>638</v>
       </c>
       <c r="AT94" t="n">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="95">
@@ -15088,10 +15088,10 @@
         </is>
       </c>
       <c r="AO95" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP95" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.42104988415376</v>
@@ -15105,7 +15105,7 @@
         <v>658</v>
       </c>
       <c r="AT95" t="n">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="96">
@@ -15242,10 +15242,10 @@
         </is>
       </c>
       <c r="AO96" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP96" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ96" t="n">
         <v>2.781853924437765</v>
@@ -15259,7 +15259,7 @@
         <v>670</v>
       </c>
       <c r="AT96" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="97">
@@ -15396,10 +15396,10 @@
         </is>
       </c>
       <c r="AO97" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP97" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ97" t="n">
         <v>3.284617664406213</v>
@@ -15413,7 +15413,7 @@
         <v>670</v>
       </c>
       <c r="AT97" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="98">
@@ -15550,10 +15550,10 @@
         </is>
       </c>
       <c r="AO98" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP98" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.6376579115357389</v>
@@ -15567,7 +15567,7 @@
         <v>670</v>
       </c>
       <c r="AT98" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="99">
@@ -15704,10 +15704,10 @@
         </is>
       </c>
       <c r="AO99" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP99" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ99" t="n">
         <v>3.370967741935484</v>
@@ -15721,7 +15721,7 @@
         <v>670</v>
       </c>
       <c r="AT99" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="100">
@@ -15858,10 +15858,10 @@
         </is>
       </c>
       <c r="AO100" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP100" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ100" t="n">
         <v>4.345000892593041</v>
@@ -15875,7 +15875,7 @@
         <v>670</v>
       </c>
       <c r="AT100" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="101">
@@ -16012,10 +16012,10 @@
         </is>
       </c>
       <c r="AO101" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP101" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.5227074697151799</v>
@@ -16029,7 +16029,7 @@
         <v>670</v>
       </c>
       <c r="AT101" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="102">
@@ -16166,10 +16166,10 @@
         </is>
       </c>
       <c r="AO102" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP102" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ102" t="n">
         <v>2.547706685837527</v>
@@ -16183,7 +16183,7 @@
         <v>670</v>
       </c>
       <c r="AT102" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="103">
@@ -16320,10 +16320,10 @@
         </is>
       </c>
       <c r="AO103" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP103" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ103" t="n">
         <v>3.178597316969029</v>
@@ -16337,7 +16337,7 @@
         <v>670</v>
       </c>
       <c r="AT103" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="104">
@@ -16474,10 +16474,10 @@
         </is>
       </c>
       <c r="AO104" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP104" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ104" t="n">
         <v>3.415388252732751</v>
@@ -16491,7 +16491,7 @@
         <v>670</v>
       </c>
       <c r="AT104" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="105">
@@ -16628,10 +16628,10 @@
         </is>
       </c>
       <c r="AO105" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP105" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.2085254965039268</v>
@@ -16645,7 +16645,7 @@
         <v>670</v>
       </c>
       <c r="AT105" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="106">
@@ -16782,10 +16782,10 @@
         </is>
       </c>
       <c r="AO106" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP106" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.3501849493035709</v>
@@ -16799,7 +16799,7 @@
         <v>670</v>
       </c>
       <c r="AT106" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="107">
@@ -16936,10 +16936,10 @@
         </is>
       </c>
       <c r="AO107" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP107" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.5901262835735002</v>
@@ -16953,7 +16953,7 @@
         <v>670</v>
       </c>
       <c r="AT107" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="108">
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="AO108" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP108" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.806916142649839</v>
@@ -17107,7 +17107,7 @@
         <v>670</v>
       </c>
       <c r="AT108" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="109">
@@ -17244,10 +17244,10 @@
         </is>
       </c>
       <c r="AO109" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP109" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.79</v>
@@ -17261,7 +17261,7 @@
         <v>699</v>
       </c>
       <c r="AT109" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="110">
@@ -17390,10 +17390,10 @@
         </is>
       </c>
       <c r="AO110" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP110" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.5096057833419115</v>
@@ -17407,7 +17407,7 @@
         <v>699</v>
       </c>
       <c r="AT110" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="111">
@@ -17544,10 +17544,10 @@
         </is>
       </c>
       <c r="AO111" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP111" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.40118019327803</v>
@@ -17561,7 +17561,7 @@
         <v>699</v>
       </c>
       <c r="AT111" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="112">
@@ -17698,10 +17698,10 @@
         </is>
       </c>
       <c r="AO112" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP112" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.3387533385057451</v>
@@ -17715,7 +17715,7 @@
         <v>699</v>
       </c>
       <c r="AT112" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="113">
@@ -17852,10 +17852,10 @@
         </is>
       </c>
       <c r="AO113" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP113" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.8189643681467087</v>
@@ -17869,7 +17869,7 @@
         <v>699</v>
       </c>
       <c r="AT113" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="114">
@@ -18006,10 +18006,10 @@
         </is>
       </c>
       <c r="AO114" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP114" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.7825758553553672</v>
@@ -18023,7 +18023,7 @@
         <v>699</v>
       </c>
       <c r="AT114" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="115">
@@ -18160,10 +18160,10 @@
         </is>
       </c>
       <c r="AO115" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP115" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.28</v>
@@ -18177,7 +18177,7 @@
         <v>714</v>
       </c>
       <c r="AT115" t="n">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="116">
@@ -18314,10 +18314,10 @@
         </is>
       </c>
       <c r="AO116" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP116" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.4907771516601127</v>
@@ -18331,7 +18331,7 @@
         <v>723</v>
       </c>
       <c r="AT116" t="n">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="117">
@@ -18468,10 +18468,10 @@
         </is>
       </c>
       <c r="AO117" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP117" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.6819402595885639</v>
@@ -18485,7 +18485,7 @@
         <v>723</v>
       </c>
       <c r="AT117" t="n">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="118">
@@ -18622,10 +18622,10 @@
         </is>
       </c>
       <c r="AO118" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP118" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.4334870412211518</v>
@@ -18639,7 +18639,7 @@
         <v>723</v>
       </c>
       <c r="AT118" t="n">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="119">
@@ -18776,10 +18776,10 @@
         </is>
       </c>
       <c r="AO119" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP119" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.3441299735854088</v>
@@ -18793,7 +18793,7 @@
         <v>723</v>
       </c>
       <c r="AT119" t="n">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="120">
@@ -18930,10 +18930,10 @@
         </is>
       </c>
       <c r="AO120" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP120" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.129165567292806</v>
@@ -18947,7 +18947,7 @@
         <v>760</v>
       </c>
       <c r="AT120" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="121">
@@ -19084,10 +19084,10 @@
         </is>
       </c>
       <c r="AO121" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP121" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.1349580585398</v>
@@ -19101,7 +19101,7 @@
         <v>760</v>
       </c>
       <c r="AT121" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="122">
@@ -19238,10 +19238,10 @@
         </is>
       </c>
       <c r="AO122" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP122" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.8253710688819983</v>
@@ -19255,7 +19255,7 @@
         <v>760</v>
       </c>
       <c r="AT122" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="123">
@@ -19392,10 +19392,10 @@
         </is>
       </c>
       <c r="AO123" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP123" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.5444014534143011</v>
@@ -19409,7 +19409,7 @@
         <v>760</v>
       </c>
       <c r="AT123" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="124">
@@ -19546,10 +19546,10 @@
         </is>
       </c>
       <c r="AO124" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP124" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.9830971446746872</v>
@@ -19563,7 +19563,7 @@
         <v>760</v>
       </c>
       <c r="AT124" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="125">
@@ -19700,10 +19700,10 @@
         </is>
       </c>
       <c r="AO125" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP125" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.245473022344757</v>
@@ -19846,10 +19846,10 @@
         </is>
       </c>
       <c r="AO126" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP126" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AQ126" t="n">
         <v>2.466370766053387</v>
@@ -20000,10 +20000,10 @@
         </is>
       </c>
       <c r="AO127" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP127" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.6666659046800456</v>
@@ -20154,10 +20154,10 @@
         </is>
       </c>
       <c r="AO128" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP128" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AQ128" t="n">
         <v>2.012449744103836</v>
@@ -20308,10 +20308,10 @@
         </is>
       </c>
       <c r="AO129" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP129" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.8197702912036356</v>
@@ -20462,10 +20462,10 @@
         </is>
       </c>
       <c r="AO130" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP130" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.6464884935644318</v>
@@ -20616,10 +20616,10 @@
         </is>
       </c>
       <c r="AO131" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP131" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.2820795698372981</v>
@@ -20770,10 +20770,10 @@
         </is>
       </c>
       <c r="AO132" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP132" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.090911258352786</v>
@@ -20924,10 +20924,10 @@
         </is>
       </c>
       <c r="AO133" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP133" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.2949960514035466</v>
@@ -21078,10 +21078,10 @@
         </is>
       </c>
       <c r="AO134" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP134" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AQ134" t="n">
         <v>1.564099411167967</v>
@@ -21232,10 +21232,10 @@
         </is>
       </c>
       <c r="AO135" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP135" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.127819613568277</v>
@@ -21386,10 +21386,10 @@
         </is>
       </c>
       <c r="AO136" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP136" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.2977589363466595</v>
@@ -21540,10 +21540,10 @@
         </is>
       </c>
       <c r="AO137" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP137" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.892102378361448</v>
@@ -21694,10 +21694,10 @@
         </is>
       </c>
       <c r="AO138" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP138" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.06188616970805819</v>
@@ -21848,10 +21848,10 @@
         </is>
       </c>
       <c r="AO139" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP139" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AQ139" t="n">
         <v>3.404252167578744</v>
@@ -22002,10 +22002,10 @@
         </is>
       </c>
       <c r="AO140" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP140" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.06060622324241086</v>
@@ -22156,10 +22156,10 @@
         </is>
       </c>
       <c r="AO141" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP141" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.747713375714869</v>
@@ -22310,10 +22310,10 @@
         </is>
       </c>
       <c r="AO142" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP142" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.6666669315762411</v>
@@ -22464,10 +22464,10 @@
         </is>
       </c>
       <c r="AO143" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP143" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.630252424097102</v>
@@ -22618,10 +22618,10 @@
         </is>
       </c>
       <c r="AO144" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP144" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.3495620695319793</v>
@@ -22772,10 +22772,10 @@
         </is>
       </c>
       <c r="AO145" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP145" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.433334350585938</v>
@@ -22926,10 +22926,10 @@
         </is>
       </c>
       <c r="AO146" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP146" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AQ146" t="n">
         <v>2.126830357558221</v>
@@ -23080,10 +23080,10 @@
         </is>
       </c>
       <c r="AO147" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP147" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.248061602881425</v>
@@ -23226,10 +23226,10 @@
         </is>
       </c>
       <c r="AO148" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP148" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.125891969160556</v>
@@ -23380,10 +23380,10 @@
         </is>
       </c>
       <c r="AO149" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP149" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.534643721725534</v>
@@ -23534,10 +23534,10 @@
         </is>
       </c>
       <c r="AO150" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP150" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.605504362403189</v>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AO151" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP151" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AQ151" t="n">
         <v>3.762685814621029</v>
@@ -23842,10 +23842,10 @@
         </is>
       </c>
       <c r="AO152" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP152" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AQ152" t="n">
         <v>4.658164039844142</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="AO153" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP153" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AQ153" t="n">
         <v>2.955077175151201</v>
@@ -24150,10 +24150,10 @@
         </is>
       </c>
       <c r="AO154" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP154" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.074688271249283</v>
@@ -24304,10 +24304,10 @@
         </is>
       </c>
       <c r="AO155" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP155" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AQ155" t="n">
         <v>2.355554613656593</v>
@@ -24321,7 +24321,7 @@
         <v>1057</v>
       </c>
       <c r="AT155" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="156">
@@ -24458,10 +24458,10 @@
         </is>
       </c>
       <c r="AO156" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP156" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.094017640208093</v>
@@ -24475,7 +24475,7 @@
         <v>1064</v>
       </c>
       <c r="AT156" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="157">
@@ -24612,10 +24612,10 @@
         </is>
       </c>
       <c r="AO157" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP157" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AQ157" t="n">
         <v>5.82341133782317</v>
@@ -24629,7 +24629,7 @@
         <v>1064</v>
       </c>
       <c r="AT157" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="158">
@@ -24766,10 +24766,10 @@
         </is>
       </c>
       <c r="AO158" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP158" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.624050388902179</v>
@@ -24783,7 +24783,7 @@
         <v>1064</v>
       </c>
       <c r="AT158" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="159">
@@ -24920,10 +24920,10 @@
         </is>
       </c>
       <c r="AO159" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP159" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AQ159" t="n">
         <v>1.166304147222442</v>
@@ -24937,7 +24937,7 @@
         <v>1064</v>
       </c>
       <c r="AT159" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="160">
@@ -25074,10 +25074,10 @@
         </is>
       </c>
       <c r="AO160" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP160" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.443849324860223</v>
@@ -25228,10 +25228,10 @@
         </is>
       </c>
       <c r="AO161" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP161" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.904762721716735</v>
@@ -25382,10 +25382,10 @@
         </is>
       </c>
       <c r="AO162" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP162" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.532534685025998</v>
@@ -25536,10 +25536,10 @@
         </is>
       </c>
       <c r="AO163" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP163" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.149532301566854</v>
@@ -25690,10 +25690,10 @@
         </is>
       </c>
       <c r="AO164" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP164" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AQ164" t="n">
         <v>2.694580031100108</v>
@@ -25844,10 +25844,10 @@
         </is>
       </c>
       <c r="AO165" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AP165" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AQ165" t="n">
         <v>2.752646056285696</v>
